--- a/data_cache/excel/E2E_historical.xlsx
+++ b/data_cache/excel/E2E_historical.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:G317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,15 +429,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>traded_quantity</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>delivery_quantity</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>delivery_pct</t>
         </is>
@@ -446,2603 +456,7900 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3048.3</v>
+        <v>2187.45</v>
       </c>
       <c r="C2" t="n">
-        <v>39410</v>
+        <v>2187.45</v>
       </c>
       <c r="D2" t="n">
-        <v>19763</v>
+        <v>2187.45</v>
       </c>
       <c r="E2" t="n">
-        <v>50.15</v>
+        <v>162326</v>
+      </c>
+      <c r="F2" t="n">
+        <v>68134</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41.97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3113.3</v>
+        <v>2078.1</v>
       </c>
       <c r="C3" t="n">
-        <v>55655</v>
+        <v>2078.1</v>
       </c>
       <c r="D3" t="n">
-        <v>28457</v>
+        <v>2078.1</v>
       </c>
       <c r="E3" t="n">
-        <v>51.13</v>
+        <v>14724</v>
+      </c>
+      <c r="F3" t="n">
+        <v>14724</v>
+      </c>
+      <c r="G3" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3047.9</v>
+        <v>2129.5</v>
       </c>
       <c r="C4" t="n">
-        <v>101280</v>
+        <v>2129.5</v>
       </c>
       <c r="D4" t="n">
-        <v>49288</v>
+        <v>2129.5</v>
       </c>
       <c r="E4" t="n">
-        <v>48.67</v>
+        <v>287140</v>
+      </c>
+      <c r="F4" t="n">
+        <v>166053</v>
+      </c>
+      <c r="G4" t="n">
+        <v>57.83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3077.2</v>
+        <v>2148.55</v>
       </c>
       <c r="C5" t="n">
-        <v>92269</v>
+        <v>2148.55</v>
       </c>
       <c r="D5" t="n">
-        <v>38877</v>
+        <v>2148.55</v>
       </c>
       <c r="E5" t="n">
-        <v>42.13</v>
+        <v>117828</v>
+      </c>
+      <c r="F5" t="n">
+        <v>48117</v>
+      </c>
+      <c r="G5" t="n">
+        <v>40.84</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3048.7</v>
+        <v>2041.15</v>
       </c>
       <c r="C6" t="n">
-        <v>72690</v>
+        <v>2041.15</v>
       </c>
       <c r="D6" t="n">
-        <v>37568</v>
+        <v>2041.15</v>
       </c>
       <c r="E6" t="n">
-        <v>51.68</v>
+        <v>106020</v>
+      </c>
+      <c r="F6" t="n">
+        <v>63772</v>
+      </c>
+      <c r="G6" t="n">
+        <v>60.15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2924.6</v>
+        <v>2037.75</v>
       </c>
       <c r="C7" t="n">
-        <v>276383</v>
+        <v>2037.75</v>
       </c>
       <c r="D7" t="n">
-        <v>97725</v>
+        <v>2037.75</v>
       </c>
       <c r="E7" t="n">
-        <v>35.36</v>
+        <v>152085</v>
+      </c>
+      <c r="F7" t="n">
+        <v>85037</v>
+      </c>
+      <c r="G7" t="n">
+        <v>55.91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2915.5</v>
+        <v>2001.7</v>
       </c>
       <c r="C8" t="n">
-        <v>330298</v>
+        <v>2001.7</v>
       </c>
       <c r="D8" t="n">
-        <v>140770</v>
+        <v>2001.7</v>
       </c>
       <c r="E8" t="n">
-        <v>42.62</v>
+        <v>40341</v>
+      </c>
+      <c r="F8" t="n">
+        <v>21978</v>
+      </c>
+      <c r="G8" t="n">
+        <v>54.48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2812.1</v>
+        <v>2101.75</v>
       </c>
       <c r="C9" t="n">
-        <v>81797</v>
+        <v>2101.75</v>
       </c>
       <c r="D9" t="n">
-        <v>35048</v>
+        <v>2101.75</v>
       </c>
       <c r="E9" t="n">
-        <v>42.85</v>
+        <v>30632</v>
+      </c>
+      <c r="F9" t="n">
+        <v>23613</v>
+      </c>
+      <c r="G9" t="n">
+        <v>77.09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2647.1</v>
+        <v>2206.8</v>
       </c>
       <c r="C10" t="n">
-        <v>156734</v>
+        <v>2206.8</v>
       </c>
       <c r="D10" t="n">
-        <v>100535</v>
+        <v>2206.8</v>
       </c>
       <c r="E10" t="n">
-        <v>64.14</v>
+        <v>57935</v>
+      </c>
+      <c r="F10" t="n">
+        <v>29540</v>
+      </c>
+      <c r="G10" t="n">
+        <v>50.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2611.6</v>
+        <v>2194.1</v>
       </c>
       <c r="C11" t="n">
-        <v>135780</v>
+        <v>2194.1</v>
       </c>
       <c r="D11" t="n">
-        <v>62952</v>
+        <v>2194.1</v>
       </c>
       <c r="E11" t="n">
-        <v>46.36</v>
+        <v>123962</v>
+      </c>
+      <c r="F11" t="n">
+        <v>59133</v>
+      </c>
+      <c r="G11" t="n">
+        <v>47.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2588.9</v>
+        <v>2084.4</v>
       </c>
       <c r="C12" t="n">
-        <v>137808</v>
+        <v>2084.4</v>
       </c>
       <c r="D12" t="n">
-        <v>54051</v>
+        <v>2084.4</v>
       </c>
       <c r="E12" t="n">
-        <v>39.22</v>
+        <v>188175</v>
+      </c>
+      <c r="F12" t="n">
+        <v>56086</v>
+      </c>
+      <c r="G12" t="n">
+        <v>29.81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2603.6</v>
+        <v>1987.85</v>
       </c>
       <c r="C13" t="n">
-        <v>73560</v>
+        <v>1987.85</v>
       </c>
       <c r="D13" t="n">
-        <v>33595</v>
+        <v>1987.85</v>
       </c>
       <c r="E13" t="n">
-        <v>45.67</v>
+        <v>114131</v>
+      </c>
+      <c r="F13" t="n">
+        <v>61506</v>
+      </c>
+      <c r="G13" t="n">
+        <v>53.89</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2585.7</v>
+        <v>1893</v>
       </c>
       <c r="C14" t="n">
-        <v>78341</v>
+        <v>1893</v>
       </c>
       <c r="D14" t="n">
-        <v>31427</v>
+        <v>1893</v>
       </c>
       <c r="E14" t="n">
-        <v>40.12</v>
+        <v>114207</v>
+      </c>
+      <c r="F14" t="n">
+        <v>60463</v>
+      </c>
+      <c r="G14" t="n">
+        <v>52.94</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2479.2</v>
+        <v>1810.9</v>
       </c>
       <c r="C15" t="n">
-        <v>59011</v>
+        <v>1810.9</v>
       </c>
       <c r="D15" t="n">
-        <v>29062</v>
+        <v>1810.9</v>
       </c>
       <c r="E15" t="n">
-        <v>49.25</v>
+        <v>255650</v>
+      </c>
+      <c r="F15" t="n">
+        <v>152970</v>
+      </c>
+      <c r="G15" t="n">
+        <v>59.84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2328.4</v>
+        <v>1876.15</v>
       </c>
       <c r="C16" t="n">
-        <v>115582</v>
+        <v>1876.15</v>
       </c>
       <c r="D16" t="n">
-        <v>59910</v>
+        <v>1876.15</v>
       </c>
       <c r="E16" t="n">
-        <v>51.83</v>
+        <v>150921</v>
+      </c>
+      <c r="F16" t="n">
+        <v>40824</v>
+      </c>
+      <c r="G16" t="n">
+        <v>27.05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2325.8</v>
+        <v>1901.95</v>
       </c>
       <c r="C17" t="n">
-        <v>103188</v>
+        <v>1901.95</v>
       </c>
       <c r="D17" t="n">
-        <v>39607</v>
+        <v>1901.95</v>
       </c>
       <c r="E17" t="n">
-        <v>38.38</v>
+        <v>150861</v>
+      </c>
+      <c r="F17" t="n">
+        <v>52347</v>
+      </c>
+      <c r="G17" t="n">
+        <v>34.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2345.7</v>
+        <v>1997</v>
       </c>
       <c r="C18" t="n">
-        <v>76864</v>
+        <v>1997</v>
       </c>
       <c r="D18" t="n">
-        <v>24656</v>
+        <v>1997</v>
       </c>
       <c r="E18" t="n">
-        <v>32.08</v>
+        <v>46416</v>
+      </c>
+      <c r="F18" t="n">
+        <v>28003</v>
+      </c>
+      <c r="G18" t="n">
+        <v>60.33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2310.2</v>
+        <v>1988.95</v>
       </c>
       <c r="C19" t="n">
-        <v>60856</v>
+        <v>1988.95</v>
       </c>
       <c r="D19" t="n">
-        <v>27273</v>
+        <v>1988.95</v>
       </c>
       <c r="E19" t="n">
-        <v>44.82</v>
+        <v>196127</v>
+      </c>
+      <c r="F19" t="n">
+        <v>76823</v>
+      </c>
+      <c r="G19" t="n">
+        <v>39.17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2261.8</v>
+        <v>1922.1</v>
       </c>
       <c r="C20" t="n">
-        <v>70341</v>
+        <v>1922.1</v>
       </c>
       <c r="D20" t="n">
-        <v>38709</v>
+        <v>1922.1</v>
       </c>
       <c r="E20" t="n">
-        <v>55.03</v>
+        <v>91620</v>
+      </c>
+      <c r="F20" t="n">
+        <v>45162</v>
+      </c>
+      <c r="G20" t="n">
+        <v>49.29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2290.1</v>
+        <v>1826</v>
       </c>
       <c r="C21" t="n">
-        <v>83064</v>
+        <v>1826</v>
       </c>
       <c r="D21" t="n">
-        <v>29690</v>
+        <v>1826</v>
       </c>
       <c r="E21" t="n">
-        <v>35.74</v>
+        <v>58866</v>
+      </c>
+      <c r="F21" t="n">
+        <v>35800</v>
+      </c>
+      <c r="G21" t="n">
+        <v>60.82</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2203.8</v>
+        <v>1741.25</v>
       </c>
       <c r="C22" t="n">
-        <v>62835</v>
+        <v>1741.25</v>
       </c>
       <c r="D22" t="n">
-        <v>34058</v>
+        <v>1741.25</v>
       </c>
       <c r="E22" t="n">
-        <v>54.2</v>
+        <v>111802</v>
+      </c>
+      <c r="F22" t="n">
+        <v>47216</v>
+      </c>
+      <c r="G22" t="n">
+        <v>42.23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2142.4</v>
+        <v>1811.65</v>
       </c>
       <c r="C23" t="n">
-        <v>141444</v>
+        <v>1811.65</v>
       </c>
       <c r="D23" t="n">
-        <v>84801</v>
+        <v>1811.65</v>
       </c>
       <c r="E23" t="n">
-        <v>59.95</v>
+        <v>85725</v>
+      </c>
+      <c r="F23" t="n">
+        <v>45792</v>
+      </c>
+      <c r="G23" t="n">
+        <v>53.42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2204.6</v>
+        <v>1810.95</v>
       </c>
       <c r="C24" t="n">
-        <v>150458</v>
+        <v>1810.95</v>
       </c>
       <c r="D24" t="n">
-        <v>56410</v>
+        <v>1810.95</v>
       </c>
       <c r="E24" t="n">
-        <v>37.49</v>
+        <v>50419</v>
+      </c>
+      <c r="F24" t="n">
+        <v>25501</v>
+      </c>
+      <c r="G24" t="n">
+        <v>50.58</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2123.8</v>
+        <v>1831.05</v>
       </c>
       <c r="C25" t="n">
-        <v>162517</v>
+        <v>1831.05</v>
       </c>
       <c r="D25" t="n">
-        <v>71086</v>
+        <v>1831.05</v>
       </c>
       <c r="E25" t="n">
-        <v>43.74</v>
+        <v>90838</v>
+      </c>
+      <c r="F25" t="n">
+        <v>50328</v>
+      </c>
+      <c r="G25" t="n">
+        <v>55.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2023</v>
+        <v>1922.6</v>
       </c>
       <c r="C26" t="n">
-        <v>121978</v>
+        <v>1922.6</v>
       </c>
       <c r="D26" t="n">
-        <v>61965</v>
+        <v>1922.6</v>
       </c>
       <c r="E26" t="n">
-        <v>50.8</v>
+        <v>92865</v>
+      </c>
+      <c r="F26" t="n">
+        <v>51492</v>
+      </c>
+      <c r="G26" t="n">
+        <v>55.45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2150.1</v>
+        <v>2018.7</v>
       </c>
       <c r="C27" t="n">
-        <v>182116</v>
+        <v>2018.7</v>
       </c>
       <c r="D27" t="n">
-        <v>59666</v>
+        <v>2018.7</v>
       </c>
       <c r="E27" t="n">
-        <v>32.76</v>
+        <v>27371</v>
+      </c>
+      <c r="F27" t="n">
+        <v>21675</v>
+      </c>
+      <c r="G27" t="n">
+        <v>79.19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2085.4</v>
       </c>
       <c r="C28" t="n">
-        <v>133417</v>
+        <v>2085.4</v>
       </c>
       <c r="D28" t="n">
-        <v>54403</v>
+        <v>2085.4</v>
       </c>
       <c r="E28" t="n">
-        <v>40.78</v>
+        <v>189424</v>
+      </c>
+      <c r="F28" t="n">
+        <v>70249</v>
+      </c>
+      <c r="G28" t="n">
+        <v>37.09</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2105.9</v>
+        <v>2189.65</v>
       </c>
       <c r="C29" t="n">
-        <v>74577</v>
+        <v>2189.65</v>
       </c>
       <c r="D29" t="n">
-        <v>29039</v>
+        <v>2189.65</v>
       </c>
       <c r="E29" t="n">
-        <v>38.94</v>
+        <v>180029</v>
+      </c>
+      <c r="F29" t="n">
+        <v>81498</v>
+      </c>
+      <c r="G29" t="n">
+        <v>45.27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2104.8</v>
+        <v>2299.1</v>
       </c>
       <c r="C30" t="n">
-        <v>84593</v>
+        <v>2299.1</v>
       </c>
       <c r="D30" t="n">
-        <v>36017</v>
+        <v>2299.1</v>
       </c>
       <c r="E30" t="n">
-        <v>42.58</v>
+        <v>47004</v>
+      </c>
+      <c r="F30" t="n">
+        <v>29482</v>
+      </c>
+      <c r="G30" t="n">
+        <v>62.72</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2102.6</v>
+        <v>2251.7</v>
       </c>
       <c r="C31" t="n">
-        <v>74138</v>
+        <v>2251.7</v>
       </c>
       <c r="D31" t="n">
-        <v>33190</v>
+        <v>2251.7</v>
       </c>
       <c r="E31" t="n">
-        <v>44.77</v>
+        <v>211886</v>
+      </c>
+      <c r="F31" t="n">
+        <v>75070</v>
+      </c>
+      <c r="G31" t="n">
+        <v>35.43</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2039.6</v>
+        <v>2139.15</v>
       </c>
       <c r="C32" t="n">
-        <v>71650</v>
+        <v>2139.15</v>
       </c>
       <c r="D32" t="n">
-        <v>42324</v>
+        <v>2139.15</v>
       </c>
       <c r="E32" t="n">
-        <v>59.07</v>
+        <v>75299</v>
+      </c>
+      <c r="F32" t="n">
+        <v>39800</v>
+      </c>
+      <c r="G32" t="n">
+        <v>52.86</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2013.8</v>
+        <v>2150.7</v>
       </c>
       <c r="C33" t="n">
-        <v>40512</v>
+        <v>2150.7</v>
       </c>
       <c r="D33" t="n">
-        <v>20631</v>
+        <v>2150.7</v>
       </c>
       <c r="E33" t="n">
-        <v>50.93</v>
+        <v>67877</v>
+      </c>
+      <c r="F33" t="n">
+        <v>28433</v>
+      </c>
+      <c r="G33" t="n">
+        <v>41.89</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2009.9</v>
+        <v>2119.8</v>
       </c>
       <c r="C34" t="n">
-        <v>49447</v>
+        <v>2119.8</v>
       </c>
       <c r="D34" t="n">
-        <v>20334</v>
+        <v>2119.8</v>
       </c>
       <c r="E34" t="n">
-        <v>41.12</v>
+        <v>57097</v>
+      </c>
+      <c r="F34" t="n">
+        <v>33907</v>
+      </c>
+      <c r="G34" t="n">
+        <v>59.38</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2063.2</v>
+        <v>2018.15</v>
       </c>
       <c r="C35" t="n">
-        <v>78269</v>
+        <v>2018.15</v>
       </c>
       <c r="D35" t="n">
-        <v>31826</v>
+        <v>2018.15</v>
       </c>
       <c r="E35" t="n">
-        <v>40.66</v>
+        <v>74455</v>
+      </c>
+      <c r="F35" t="n">
+        <v>41773</v>
+      </c>
+      <c r="G35" t="n">
+        <v>56.11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2079.7</v>
+        <v>2005.1</v>
       </c>
       <c r="C36" t="n">
-        <v>82802</v>
+        <v>2005.1</v>
       </c>
       <c r="D36" t="n">
-        <v>36430</v>
+        <v>2005.1</v>
       </c>
       <c r="E36" t="n">
-        <v>44</v>
+        <v>49592</v>
+      </c>
+      <c r="F36" t="n">
+        <v>27231</v>
+      </c>
+      <c r="G36" t="n">
+        <v>54.91</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2095.3</v>
+        <v>2021.7</v>
       </c>
       <c r="C37" t="n">
-        <v>45047</v>
+        <v>2021.7</v>
       </c>
       <c r="D37" t="n">
-        <v>20460</v>
+        <v>2021.7</v>
       </c>
       <c r="E37" t="n">
-        <v>45.42</v>
+        <v>74623</v>
+      </c>
+      <c r="F37" t="n">
+        <v>38667</v>
+      </c>
+      <c r="G37" t="n">
+        <v>51.82</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2079.4</v>
+        <v>1951.75</v>
       </c>
       <c r="C38" t="n">
-        <v>31746</v>
+        <v>1951.75</v>
       </c>
       <c r="D38" t="n">
-        <v>14611</v>
+        <v>1951.75</v>
       </c>
       <c r="E38" t="n">
-        <v>46.02</v>
+        <v>68135</v>
+      </c>
+      <c r="F38" t="n">
+        <v>42447</v>
+      </c>
+      <c r="G38" t="n">
+        <v>62.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2050.8</v>
+        <v>1854.2</v>
       </c>
       <c r="C39" t="n">
-        <v>31159</v>
+        <v>1854.2</v>
       </c>
       <c r="D39" t="n">
-        <v>17404</v>
+        <v>1854.2</v>
       </c>
       <c r="E39" t="n">
-        <v>55.86</v>
+        <v>38339</v>
+      </c>
+      <c r="F39" t="n">
+        <v>22109</v>
+      </c>
+      <c r="G39" t="n">
+        <v>57.67</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1955.2</v>
+        <v>1898.8</v>
       </c>
       <c r="C40" t="n">
-        <v>105748</v>
+        <v>1898.8</v>
       </c>
       <c r="D40" t="n">
-        <v>63026</v>
+        <v>1898.8</v>
       </c>
       <c r="E40" t="n">
-        <v>59.6</v>
+        <v>34409</v>
+      </c>
+      <c r="F40" t="n">
+        <v>19488</v>
+      </c>
+      <c r="G40" t="n">
+        <v>56.64</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1963.4</v>
+        <v>1879.6</v>
       </c>
       <c r="C41" t="n">
-        <v>116879</v>
+        <v>1879.6</v>
       </c>
       <c r="D41" t="n">
-        <v>58419</v>
+        <v>1879.6</v>
       </c>
       <c r="E41" t="n">
-        <v>49.98</v>
+        <v>29891</v>
+      </c>
+      <c r="F41" t="n">
+        <v>16066</v>
+      </c>
+      <c r="G41" t="n">
+        <v>53.75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1991.5</v>
+        <v>1899.45</v>
       </c>
       <c r="C42" t="n">
-        <v>79461</v>
+        <v>1899.45</v>
       </c>
       <c r="D42" t="n">
-        <v>36982</v>
+        <v>1899.45</v>
       </c>
       <c r="E42" t="n">
-        <v>46.54</v>
+        <v>85677</v>
+      </c>
+      <c r="F42" t="n">
+        <v>37373</v>
+      </c>
+      <c r="G42" t="n">
+        <v>43.62</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1999.2</v>
+        <v>1994.4</v>
       </c>
       <c r="C43" t="n">
-        <v>50833</v>
+        <v>1994.4</v>
       </c>
       <c r="D43" t="n">
-        <v>25748</v>
+        <v>1994.4</v>
       </c>
       <c r="E43" t="n">
-        <v>50.65</v>
+        <v>66325</v>
+      </c>
+      <c r="F43" t="n">
+        <v>31878</v>
+      </c>
+      <c r="G43" t="n">
+        <v>48.06</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2027.5</v>
+        <v>2003.2</v>
       </c>
       <c r="C44" t="n">
-        <v>86603</v>
+        <v>2003.2</v>
       </c>
       <c r="D44" t="n">
-        <v>35896</v>
+        <v>2003.2</v>
       </c>
       <c r="E44" t="n">
-        <v>41.45</v>
+        <v>42641</v>
+      </c>
+      <c r="F44" t="n">
+        <v>27337</v>
+      </c>
+      <c r="G44" t="n">
+        <v>64.11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2088.5</v>
+        <v>1903.1</v>
       </c>
       <c r="C45" t="n">
-        <v>145881</v>
+        <v>1903.1</v>
       </c>
       <c r="D45" t="n">
-        <v>57550</v>
+        <v>1903.1</v>
       </c>
       <c r="E45" t="n">
-        <v>39.45</v>
+        <v>204498</v>
+      </c>
+      <c r="F45" t="n">
+        <v>96683</v>
+      </c>
+      <c r="G45" t="n">
+        <v>47.28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2035.6</v>
+        <v>1808</v>
       </c>
       <c r="C46" t="n">
-        <v>71808</v>
+        <v>1808</v>
       </c>
       <c r="D46" t="n">
-        <v>26914</v>
+        <v>1808</v>
       </c>
       <c r="E46" t="n">
-        <v>37.48</v>
+        <v>221125</v>
+      </c>
+      <c r="F46" t="n">
+        <v>117736</v>
+      </c>
+      <c r="G46" t="n">
+        <v>53.24</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2024.7</v>
+        <v>1898.4</v>
       </c>
       <c r="C47" t="n">
-        <v>57473</v>
+        <v>1898.4</v>
       </c>
       <c r="D47" t="n">
-        <v>25650</v>
+        <v>1898.4</v>
       </c>
       <c r="E47" t="n">
-        <v>44.63</v>
+        <v>346022</v>
+      </c>
+      <c r="F47" t="n">
+        <v>185895</v>
+      </c>
+      <c r="G47" t="n">
+        <v>53.72</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2036.8</v>
+        <v>1993.3</v>
       </c>
       <c r="C48" t="n">
-        <v>222062</v>
+        <v>1993.3</v>
       </c>
       <c r="D48" t="n">
-        <v>62563</v>
+        <v>1993.3</v>
       </c>
       <c r="E48" t="n">
-        <v>28.17</v>
+        <v>140810</v>
+      </c>
+      <c r="F48" t="n">
+        <v>64597</v>
+      </c>
+      <c r="G48" t="n">
+        <v>45.88</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2037.3</v>
+        <v>2092.9</v>
       </c>
       <c r="C49" t="n">
-        <v>158036</v>
+        <v>2092.9</v>
       </c>
       <c r="D49" t="n">
-        <v>50017</v>
+        <v>2092.9</v>
       </c>
       <c r="E49" t="n">
-        <v>31.65</v>
+        <v>54621</v>
+      </c>
+      <c r="F49" t="n">
+        <v>41997</v>
+      </c>
+      <c r="G49" t="n">
+        <v>76.89</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2025.4</v>
+        <v>2197.5</v>
       </c>
       <c r="C50" t="n">
-        <v>201317</v>
+        <v>2197.5</v>
       </c>
       <c r="D50" t="n">
-        <v>45184</v>
+        <v>2197.5</v>
       </c>
       <c r="E50" t="n">
-        <v>22.44</v>
+        <v>497291</v>
+      </c>
+      <c r="F50" t="n">
+        <v>257273</v>
+      </c>
+      <c r="G50" t="n">
+        <v>51.73</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1987.8</v>
+        <v>2307.3</v>
       </c>
       <c r="C51" t="n">
-        <v>49426</v>
+        <v>2307.3</v>
       </c>
       <c r="D51" t="n">
-        <v>19714</v>
+        <v>2307.3</v>
       </c>
       <c r="E51" t="n">
-        <v>39.89</v>
+        <v>31072</v>
+      </c>
+      <c r="F51" t="n">
+        <v>30572</v>
+      </c>
+      <c r="G51" t="n">
+        <v>98.39</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2024.1</v>
+        <v>2422.6</v>
       </c>
       <c r="C52" t="n">
-        <v>179768</v>
+        <v>2422.6</v>
       </c>
       <c r="D52" t="n">
-        <v>48913</v>
+        <v>2422.6</v>
       </c>
       <c r="E52" t="n">
-        <v>27.21</v>
+        <v>93605</v>
+      </c>
+      <c r="F52" t="n">
+        <v>33203</v>
+      </c>
+      <c r="G52" t="n">
+        <v>35.47</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2024.1</v>
+        <v>2414.9</v>
       </c>
       <c r="C53" t="n">
-        <v>179768</v>
+        <v>2414.9</v>
       </c>
       <c r="D53" t="n">
-        <v>48913</v>
+        <v>2414.9</v>
       </c>
       <c r="E53" t="n">
-        <v>27.21</v>
+        <v>208901</v>
+      </c>
+      <c r="F53" t="n">
+        <v>111183</v>
+      </c>
+      <c r="G53" t="n">
+        <v>53.22</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2226.5</v>
+        <v>2521.4</v>
       </c>
       <c r="C54" t="n">
-        <v>302113</v>
+        <v>2521.4</v>
       </c>
       <c r="D54" t="n">
-        <v>122871</v>
+        <v>2521.4</v>
       </c>
       <c r="E54" t="n">
-        <v>40.67</v>
+        <v>132139</v>
+      </c>
+      <c r="F54" t="n">
+        <v>70407</v>
+      </c>
+      <c r="G54" t="n">
+        <v>53.28</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2243.2</v>
+        <v>2647.4</v>
       </c>
       <c r="C55" t="n">
-        <v>310507</v>
+        <v>2647.4</v>
       </c>
       <c r="D55" t="n">
-        <v>94825</v>
+        <v>2647.4</v>
       </c>
       <c r="E55" t="n">
-        <v>30.54</v>
+        <v>89055</v>
+      </c>
+      <c r="F55" t="n">
+        <v>58355</v>
+      </c>
+      <c r="G55" t="n">
+        <v>65.53</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2149.9</v>
+        <v>2567.9</v>
       </c>
       <c r="C56" t="n">
-        <v>153299</v>
+        <v>2567.9</v>
       </c>
       <c r="D56" t="n">
-        <v>43501</v>
+        <v>2567.9</v>
       </c>
       <c r="E56" t="n">
-        <v>28.38</v>
+        <v>163726</v>
+      </c>
+      <c r="F56" t="n">
+        <v>90933</v>
+      </c>
+      <c r="G56" t="n">
+        <v>55.54</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2064.3</v>
+        <v>2696.2</v>
       </c>
       <c r="C57" t="n">
-        <v>114485</v>
+        <v>2696.2</v>
       </c>
       <c r="D57" t="n">
-        <v>33699</v>
+        <v>2696.2</v>
       </c>
       <c r="E57" t="n">
-        <v>29.44</v>
+        <v>86039</v>
+      </c>
+      <c r="F57" t="n">
+        <v>45517</v>
+      </c>
+      <c r="G57" t="n">
+        <v>52.9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2081.3</v>
+        <v>2811.2</v>
       </c>
       <c r="C58" t="n">
-        <v>64892</v>
+        <v>2811.2</v>
       </c>
       <c r="D58" t="n">
-        <v>26695</v>
+        <v>2811.2</v>
       </c>
       <c r="E58" t="n">
-        <v>41.14</v>
+        <v>128352</v>
+      </c>
+      <c r="F58" t="n">
+        <v>62601</v>
+      </c>
+      <c r="G58" t="n">
+        <v>48.77</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2030.5</v>
+        <v>2671.5</v>
       </c>
       <c r="C59" t="n">
-        <v>46918</v>
+        <v>2671.5</v>
       </c>
       <c r="D59" t="n">
-        <v>23107</v>
+        <v>2671.5</v>
       </c>
       <c r="E59" t="n">
-        <v>49.25</v>
+        <v>219088</v>
+      </c>
+      <c r="F59" t="n">
+        <v>107628</v>
+      </c>
+      <c r="G59" t="n">
+        <v>49.13</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2039.8</v>
+        <v>2805</v>
       </c>
       <c r="C60" t="n">
-        <v>55625</v>
+        <v>2805</v>
       </c>
       <c r="D60" t="n">
-        <v>19253</v>
+        <v>2805</v>
       </c>
       <c r="E60" t="n">
-        <v>34.61</v>
+        <v>132496</v>
+      </c>
+      <c r="F60" t="n">
+        <v>79085</v>
+      </c>
+      <c r="G60" t="n">
+        <v>59.69</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2076.4</v>
+        <v>2871.6</v>
       </c>
       <c r="C61" t="n">
-        <v>45375</v>
+        <v>2871.6</v>
       </c>
       <c r="D61" t="n">
-        <v>20377</v>
+        <v>2871.6</v>
       </c>
       <c r="E61" t="n">
-        <v>44.91</v>
+        <v>164151</v>
+      </c>
+      <c r="F61" t="n">
+        <v>81362</v>
+      </c>
+      <c r="G61" t="n">
+        <v>49.57</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2041.4</v>
+        <v>2807.9</v>
       </c>
       <c r="C62" t="n">
-        <v>52141</v>
+        <v>2807.9</v>
       </c>
       <c r="D62" t="n">
-        <v>21577</v>
+        <v>2807.9</v>
       </c>
       <c r="E62" t="n">
-        <v>41.38</v>
+        <v>112733</v>
+      </c>
+      <c r="F62" t="n">
+        <v>63677</v>
+      </c>
+      <c r="G62" t="n">
+        <v>56.48</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2122.4</v>
+        <v>2843.8</v>
       </c>
       <c r="C63" t="n">
-        <v>74795</v>
+        <v>2843.8</v>
       </c>
       <c r="D63" t="n">
-        <v>31479</v>
+        <v>2843.8</v>
       </c>
       <c r="E63" t="n">
-        <v>42.09</v>
+        <v>97787</v>
+      </c>
+      <c r="F63" t="n">
+        <v>50746</v>
+      </c>
+      <c r="G63" t="n">
+        <v>51.89</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2439.1</v>
+        <v>2822.1</v>
       </c>
       <c r="C64" t="n">
-        <v>458044</v>
+        <v>2822.1</v>
       </c>
       <c r="D64" t="n">
-        <v>143026</v>
+        <v>2822.1</v>
       </c>
       <c r="E64" t="n">
-        <v>31.23</v>
+        <v>143084</v>
+      </c>
+      <c r="F64" t="n">
+        <v>57045</v>
+      </c>
+      <c r="G64" t="n">
+        <v>39.87</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2601.2</v>
+        <v>2768.8</v>
       </c>
       <c r="C65" t="n">
-        <v>218995</v>
+        <v>2768.8</v>
       </c>
       <c r="D65" t="n">
-        <v>77037</v>
+        <v>2768.8</v>
       </c>
       <c r="E65" t="n">
-        <v>35.18</v>
+        <v>84735</v>
+      </c>
+      <c r="F65" t="n">
+        <v>45928</v>
+      </c>
+      <c r="G65" t="n">
+        <v>54.2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2452.4</v>
+        <v>2742.5</v>
       </c>
       <c r="C66" t="n">
-        <v>177590</v>
+        <v>2742.5</v>
       </c>
       <c r="D66" t="n">
-        <v>68733</v>
+        <v>2742.5</v>
       </c>
       <c r="E66" t="n">
-        <v>38.7</v>
+        <v>87689</v>
+      </c>
+      <c r="F66" t="n">
+        <v>49742</v>
+      </c>
+      <c r="G66" t="n">
+        <v>56.73</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2366.9</v>
+        <v>2865.6</v>
       </c>
       <c r="C67" t="n">
-        <v>75624</v>
+        <v>2865.6</v>
       </c>
       <c r="D67" t="n">
-        <v>26056</v>
+        <v>2865.6</v>
       </c>
       <c r="E67" t="n">
-        <v>34.45</v>
+        <v>94015</v>
+      </c>
+      <c r="F67" t="n">
+        <v>58633</v>
+      </c>
+      <c r="G67" t="n">
+        <v>62.37</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2498.1</v>
+        <v>2918</v>
       </c>
       <c r="C68" t="n">
-        <v>203107</v>
+        <v>2918</v>
       </c>
       <c r="D68" t="n">
-        <v>44047</v>
+        <v>2918</v>
       </c>
       <c r="E68" t="n">
-        <v>21.69</v>
+        <v>72085</v>
+      </c>
+      <c r="F68" t="n">
+        <v>34915</v>
+      </c>
+      <c r="G68" t="n">
+        <v>48.44</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2634.4</v>
+        <v>2998.7</v>
       </c>
       <c r="C69" t="n">
-        <v>178763</v>
+        <v>2998.7</v>
       </c>
       <c r="D69" t="n">
-        <v>58925</v>
+        <v>2998.7</v>
       </c>
       <c r="E69" t="n">
-        <v>32.96</v>
+        <v>144104</v>
+      </c>
+      <c r="F69" t="n">
+        <v>55301</v>
+      </c>
+      <c r="G69" t="n">
+        <v>38.38</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2580.5</v>
+        <v>2923</v>
       </c>
       <c r="C70" t="n">
-        <v>90959</v>
+        <v>2923</v>
       </c>
       <c r="D70" t="n">
-        <v>34711</v>
+        <v>2923</v>
       </c>
       <c r="E70" t="n">
-        <v>38.16</v>
+        <v>60141</v>
+      </c>
+      <c r="F70" t="n">
+        <v>35738</v>
+      </c>
+      <c r="G70" t="n">
+        <v>59.42</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2632.8</v>
+        <v>2863.9</v>
       </c>
       <c r="C71" t="n">
-        <v>100164</v>
+        <v>2863.9</v>
       </c>
       <c r="D71" t="n">
-        <v>28358</v>
+        <v>2863.9</v>
       </c>
       <c r="E71" t="n">
-        <v>28.31</v>
+        <v>39165</v>
+      </c>
+      <c r="F71" t="n">
+        <v>20485</v>
+      </c>
+      <c r="G71" t="n">
+        <v>52.3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2550.6</v>
+        <v>2782.1</v>
       </c>
       <c r="C72" t="n">
-        <v>87937</v>
+        <v>2782.1</v>
       </c>
       <c r="D72" t="n">
-        <v>44174</v>
+        <v>2782.1</v>
       </c>
       <c r="E72" t="n">
-        <v>50.23</v>
+        <v>43174</v>
+      </c>
+      <c r="F72" t="n">
+        <v>27173</v>
+      </c>
+      <c r="G72" t="n">
+        <v>62.94</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2485.1</v>
+        <v>2828.2</v>
       </c>
       <c r="C73" t="n">
-        <v>98736</v>
+        <v>2828.2</v>
       </c>
       <c r="D73" t="n">
-        <v>37904</v>
+        <v>2828.2</v>
       </c>
       <c r="E73" t="n">
-        <v>38.39</v>
+        <v>64974</v>
+      </c>
+      <c r="F73" t="n">
+        <v>27213</v>
+      </c>
+      <c r="G73" t="n">
+        <v>41.88</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2582.8</v>
+        <v>2868.2</v>
       </c>
       <c r="C74" t="n">
-        <v>158022</v>
+        <v>2868.2</v>
       </c>
       <c r="D74" t="n">
-        <v>47279</v>
+        <v>2868.2</v>
       </c>
       <c r="E74" t="n">
-        <v>29.92</v>
+        <v>294189</v>
+      </c>
+      <c r="F74" t="n">
+        <v>153611</v>
+      </c>
+      <c r="G74" t="n">
+        <v>52.22</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2556.9</v>
+        <v>2895.6</v>
       </c>
       <c r="C75" t="n">
-        <v>67959</v>
+        <v>2895.6</v>
       </c>
       <c r="D75" t="n">
-        <v>21571</v>
+        <v>2895.6</v>
       </c>
       <c r="E75" t="n">
-        <v>31.74</v>
+        <v>63717</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32505</v>
+      </c>
+      <c r="G75" t="n">
+        <v>51.01</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2850.4</v>
+        <v>2814.8</v>
       </c>
       <c r="C76" t="n">
-        <v>2239301</v>
+        <v>2814.8</v>
       </c>
       <c r="D76" t="n">
-        <v>339828</v>
+        <v>2814.8</v>
       </c>
       <c r="E76" t="n">
-        <v>15.18</v>
+        <v>61423</v>
+      </c>
+      <c r="F76" t="n">
+        <v>40746</v>
+      </c>
+      <c r="G76" t="n">
+        <v>66.34</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2963.4</v>
+        <v>2839</v>
       </c>
       <c r="C77" t="n">
-        <v>1888814</v>
+        <v>2839</v>
       </c>
       <c r="D77" t="n">
-        <v>236614</v>
+        <v>2839</v>
       </c>
       <c r="E77" t="n">
-        <v>12.53</v>
+        <v>34469</v>
+      </c>
+      <c r="F77" t="n">
+        <v>18224</v>
+      </c>
+      <c r="G77" t="n">
+        <v>52.87</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2878.6</v>
+        <v>2803.6</v>
       </c>
       <c r="C78" t="n">
-        <v>657086</v>
+        <v>2803.6</v>
       </c>
       <c r="D78" t="n">
-        <v>127744</v>
+        <v>2803.6</v>
       </c>
       <c r="E78" t="n">
-        <v>19.44</v>
+        <v>62920</v>
+      </c>
+      <c r="F78" t="n">
+        <v>38784</v>
+      </c>
+      <c r="G78" t="n">
+        <v>61.64</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2569.5</v>
+        <v>2731</v>
       </c>
       <c r="C79" t="n">
-        <v>713255</v>
+        <v>2731</v>
       </c>
       <c r="D79" t="n">
-        <v>204884</v>
+        <v>2731</v>
       </c>
       <c r="E79" t="n">
-        <v>28.73</v>
+        <v>67837</v>
+      </c>
+      <c r="F79" t="n">
+        <v>40114</v>
+      </c>
+      <c r="G79" t="n">
+        <v>59.13</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3175.6</v>
+        <v>2677.9</v>
       </c>
       <c r="C80" t="n">
-        <v>62094</v>
+        <v>2677.9</v>
       </c>
       <c r="D80" t="n">
-        <v>37564</v>
+        <v>2677.9</v>
       </c>
       <c r="E80" t="n">
-        <v>60.5</v>
+        <v>74476</v>
+      </c>
+      <c r="F80" t="n">
+        <v>48151</v>
+      </c>
+      <c r="G80" t="n">
+        <v>64.65000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3331.4</v>
+        <v>2729.4</v>
       </c>
       <c r="C81" t="n">
-        <v>294517</v>
+        <v>2729.4</v>
       </c>
       <c r="D81" t="n">
-        <v>119385</v>
+        <v>2729.4</v>
       </c>
       <c r="E81" t="n">
-        <v>40.54</v>
+        <v>71700</v>
+      </c>
+      <c r="F81" t="n">
+        <v>35995</v>
+      </c>
+      <c r="G81" t="n">
+        <v>50.2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3409.3</v>
+        <v>2670.6</v>
       </c>
       <c r="C82" t="n">
-        <v>140353</v>
+        <v>2670.6</v>
       </c>
       <c r="D82" t="n">
-        <v>64765</v>
+        <v>2670.6</v>
       </c>
       <c r="E82" t="n">
-        <v>46.14</v>
+        <v>56997</v>
+      </c>
+      <c r="F82" t="n">
+        <v>32875</v>
+      </c>
+      <c r="G82" t="n">
+        <v>57.68</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3578.4</v>
+        <v>2649.5</v>
       </c>
       <c r="C83" t="n">
-        <v>198175</v>
+        <v>2649.5</v>
       </c>
       <c r="D83" t="n">
-        <v>109494</v>
+        <v>2649.5</v>
       </c>
       <c r="E83" t="n">
-        <v>55.25</v>
+        <v>68077</v>
+      </c>
+      <c r="F83" t="n">
+        <v>36194</v>
+      </c>
+      <c r="G83" t="n">
+        <v>53.17</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3701.8</v>
+        <v>2618.3</v>
       </c>
       <c r="C84" t="n">
-        <v>257636</v>
+        <v>2618.3</v>
       </c>
       <c r="D84" t="n">
-        <v>119673</v>
+        <v>2618.3</v>
       </c>
       <c r="E84" t="n">
-        <v>46.45</v>
+        <v>53343</v>
+      </c>
+      <c r="F84" t="n">
+        <v>27175</v>
+      </c>
+      <c r="G84" t="n">
+        <v>50.94</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3884.7</v>
+        <v>2593.6</v>
       </c>
       <c r="C85" t="n">
-        <v>228433</v>
+        <v>2593.6</v>
       </c>
       <c r="D85" t="n">
-        <v>113335</v>
+        <v>2593.6</v>
       </c>
       <c r="E85" t="n">
-        <v>49.61</v>
+        <v>54921</v>
+      </c>
+      <c r="F85" t="n">
+        <v>27292</v>
+      </c>
+      <c r="G85" t="n">
+        <v>49.69</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3951.4</v>
+        <v>2581.5</v>
       </c>
       <c r="C86" t="n">
-        <v>222973</v>
+        <v>2581.5</v>
       </c>
       <c r="D86" t="n">
-        <v>96971</v>
+        <v>2581.5</v>
       </c>
       <c r="E86" t="n">
-        <v>43.49</v>
+        <v>41028</v>
+      </c>
+      <c r="F86" t="n">
+        <v>21315</v>
+      </c>
+      <c r="G86" t="n">
+        <v>51.95</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3951.4</v>
+        <v>2594.7</v>
       </c>
       <c r="C87" t="n">
-        <v>222973</v>
+        <v>2594.7</v>
       </c>
       <c r="D87" t="n">
-        <v>96971</v>
+        <v>2594.7</v>
       </c>
       <c r="E87" t="n">
-        <v>43.49</v>
+        <v>32765</v>
+      </c>
+      <c r="F87" t="n">
+        <v>14816</v>
+      </c>
+      <c r="G87" t="n">
+        <v>45.22</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3922.4</v>
+        <v>2504</v>
       </c>
       <c r="C88" t="n">
-        <v>313538</v>
+        <v>2504</v>
       </c>
       <c r="D88" t="n">
-        <v>135873</v>
+        <v>2504</v>
       </c>
       <c r="E88" t="n">
-        <v>43.34</v>
+        <v>51264</v>
+      </c>
+      <c r="F88" t="n">
+        <v>28133</v>
+      </c>
+      <c r="G88" t="n">
+        <v>54.88</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>4118.5</v>
+        <v>2509.7</v>
       </c>
       <c r="C89" t="n">
-        <v>248727</v>
+        <v>2509.7</v>
       </c>
       <c r="D89" t="n">
-        <v>115608</v>
+        <v>2509.7</v>
       </c>
       <c r="E89" t="n">
-        <v>46.48</v>
+        <v>42576</v>
+      </c>
+      <c r="F89" t="n">
+        <v>23690</v>
+      </c>
+      <c r="G89" t="n">
+        <v>55.64</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>4324.4</v>
+        <v>2534.8</v>
       </c>
       <c r="C90" t="n">
-        <v>204649</v>
+        <v>2534.8</v>
       </c>
       <c r="D90" t="n">
-        <v>107467</v>
+        <v>2534.8</v>
       </c>
       <c r="E90" t="n">
-        <v>52.51</v>
+        <v>36938</v>
+      </c>
+      <c r="F90" t="n">
+        <v>18637</v>
+      </c>
+      <c r="G90" t="n">
+        <v>50.45</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>4108.2</v>
+        <v>2563.7</v>
       </c>
       <c r="C91" t="n">
-        <v>450792</v>
+        <v>2563.7</v>
       </c>
       <c r="D91" t="n">
-        <v>202567</v>
+        <v>2563.7</v>
       </c>
       <c r="E91" t="n">
-        <v>44.94</v>
+        <v>42679</v>
+      </c>
+      <c r="F91" t="n">
+        <v>19928</v>
+      </c>
+      <c r="G91" t="n">
+        <v>46.69</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>4313.6</v>
+        <v>2508.5</v>
       </c>
       <c r="C92" t="n">
-        <v>215019</v>
+        <v>2508.5</v>
       </c>
       <c r="D92" t="n">
-        <v>111990</v>
+        <v>2508.5</v>
       </c>
       <c r="E92" t="n">
-        <v>52.08</v>
+        <v>36852</v>
+      </c>
+      <c r="F92" t="n">
+        <v>20786</v>
+      </c>
+      <c r="G92" t="n">
+        <v>56.4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>430.3</v>
+        <v>2492.5</v>
       </c>
       <c r="C93" t="n">
-        <v>2467251</v>
+        <v>2492.5</v>
       </c>
       <c r="D93" t="n">
-        <v>1154249</v>
+        <v>2492.5</v>
       </c>
       <c r="E93" t="n">
-        <v>46.78</v>
+        <v>66636</v>
+      </c>
+      <c r="F93" t="n">
+        <v>39502</v>
+      </c>
+      <c r="G93" t="n">
+        <v>59.28</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>408.8</v>
+        <v>2617.1</v>
       </c>
       <c r="C94" t="n">
-        <v>3491521</v>
+        <v>2617.1</v>
       </c>
       <c r="D94" t="n">
-        <v>1613232</v>
+        <v>2617.1</v>
       </c>
       <c r="E94" t="n">
-        <v>46.2</v>
+        <v>134571</v>
+      </c>
+      <c r="F94" t="n">
+        <v>81852</v>
+      </c>
+      <c r="G94" t="n">
+        <v>60.82</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>388.4</v>
+        <v>2652</v>
       </c>
       <c r="C95" t="n">
-        <v>1751202</v>
+        <v>2652</v>
       </c>
       <c r="D95" t="n">
-        <v>955572</v>
+        <v>2652</v>
       </c>
       <c r="E95" t="n">
-        <v>54.57</v>
+        <v>171302</v>
+      </c>
+      <c r="F95" t="n">
+        <v>85258</v>
+      </c>
+      <c r="G95" t="n">
+        <v>49.77</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>369</v>
+        <v>2671.1</v>
       </c>
       <c r="C96" t="n">
-        <v>220311</v>
+        <v>2671.1</v>
       </c>
       <c r="D96" t="n">
-        <v>215317</v>
+        <v>2671.1</v>
       </c>
       <c r="E96" t="n">
-        <v>97.73</v>
+        <v>71743</v>
+      </c>
+      <c r="F96" t="n">
+        <v>39067</v>
+      </c>
+      <c r="G96" t="n">
+        <v>54.45</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>386.4</v>
+        <v>2594.5</v>
       </c>
       <c r="C97" t="n">
-        <v>6228077</v>
+        <v>2594.5</v>
       </c>
       <c r="D97" t="n">
-        <v>2197288</v>
+        <v>2594.5</v>
       </c>
       <c r="E97" t="n">
-        <v>35.28</v>
+        <v>57903</v>
+      </c>
+      <c r="F97" t="n">
+        <v>28896</v>
+      </c>
+      <c r="G97" t="n">
+        <v>49.9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>373.9</v>
+        <v>2543.5</v>
       </c>
       <c r="C98" t="n">
-        <v>4301429</v>
+        <v>2543.5</v>
       </c>
       <c r="D98" t="n">
-        <v>1477676</v>
+        <v>2543.5</v>
       </c>
       <c r="E98" t="n">
-        <v>34.35</v>
+        <v>41209</v>
+      </c>
+      <c r="F98" t="n">
+        <v>22695</v>
+      </c>
+      <c r="G98" t="n">
+        <v>55.07</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>382.5</v>
+        <v>2509.4</v>
       </c>
       <c r="C99" t="n">
-        <v>1386909</v>
+        <v>2509.4</v>
       </c>
       <c r="D99" t="n">
-        <v>555817</v>
+        <v>2509.4</v>
       </c>
       <c r="E99" t="n">
-        <v>40.08</v>
+        <v>37024</v>
+      </c>
+      <c r="F99" t="n">
+        <v>21080</v>
+      </c>
+      <c r="G99" t="n">
+        <v>56.94</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>386.4</v>
+        <v>2485.5</v>
       </c>
       <c r="C100" t="n">
-        <v>1236447</v>
+        <v>2485.5</v>
       </c>
       <c r="D100" t="n">
-        <v>493145</v>
+        <v>2485.5</v>
       </c>
       <c r="E100" t="n">
-        <v>39.88</v>
+        <v>30809</v>
+      </c>
+      <c r="F100" t="n">
+        <v>18969</v>
+      </c>
+      <c r="G100" t="n">
+        <v>61.57</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>405.7</v>
+        <v>2472.4</v>
       </c>
       <c r="C101" t="n">
-        <v>2392972</v>
+        <v>2472.4</v>
       </c>
       <c r="D101" t="n">
-        <v>1181927</v>
+        <v>2472.4</v>
       </c>
       <c r="E101" t="n">
-        <v>49.39</v>
+        <v>22301</v>
+      </c>
+      <c r="F101" t="n">
+        <v>12214</v>
+      </c>
+      <c r="G101" t="n">
+        <v>54.77</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>425.9</v>
+        <v>2550.5</v>
       </c>
       <c r="C102" t="n">
-        <v>558938</v>
+        <v>2550.5</v>
       </c>
       <c r="D102" t="n">
-        <v>431573</v>
+        <v>2550.5</v>
       </c>
       <c r="E102" t="n">
-        <v>77.20999999999999</v>
+        <v>75432</v>
+      </c>
+      <c r="F102" t="n">
+        <v>41024</v>
+      </c>
+      <c r="G102" t="n">
+        <v>54.39</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>447.1</v>
+        <v>2533.7</v>
       </c>
       <c r="C103" t="n">
-        <v>3014749</v>
+        <v>2533.7</v>
       </c>
       <c r="D103" t="n">
-        <v>1408417</v>
+        <v>2533.7</v>
       </c>
       <c r="E103" t="n">
-        <v>46.72</v>
+        <v>26721</v>
+      </c>
+      <c r="F103" t="n">
+        <v>17003</v>
+      </c>
+      <c r="G103" t="n">
+        <v>63.63</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>433</v>
+        <v>2502.6</v>
       </c>
       <c r="C104" t="n">
-        <v>4134531</v>
+        <v>2502.6</v>
       </c>
       <c r="D104" t="n">
-        <v>1703413</v>
+        <v>2502.6</v>
       </c>
       <c r="E104" t="n">
-        <v>41.2</v>
+        <v>18363</v>
+      </c>
+      <c r="F104" t="n">
+        <v>11373</v>
+      </c>
+      <c r="G104" t="n">
+        <v>61.93</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>418.2</v>
+        <v>2436.5</v>
       </c>
       <c r="C105" t="n">
-        <v>1672183</v>
+        <v>2436.5</v>
       </c>
       <c r="D105" t="n">
-        <v>785289</v>
+        <v>2436.5</v>
       </c>
       <c r="E105" t="n">
-        <v>46.96</v>
+        <v>36022</v>
+      </c>
+      <c r="F105" t="n">
+        <v>21694</v>
+      </c>
+      <c r="G105" t="n">
+        <v>60.22</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>412.3</v>
+        <v>2363.2</v>
       </c>
       <c r="C106" t="n">
-        <v>1439517</v>
+        <v>2363.2</v>
       </c>
       <c r="D106" t="n">
-        <v>775347</v>
+        <v>2363.2</v>
       </c>
       <c r="E106" t="n">
-        <v>53.86</v>
+        <v>63654</v>
+      </c>
+      <c r="F106" t="n">
+        <v>38600</v>
+      </c>
+      <c r="G106" t="n">
+        <v>60.64</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>412.3</v>
+        <v>2367</v>
       </c>
       <c r="C107" t="n">
-        <v>1439517</v>
+        <v>2367</v>
       </c>
       <c r="D107" t="n">
-        <v>775347</v>
+        <v>2367</v>
       </c>
       <c r="E107" t="n">
-        <v>53.86</v>
+        <v>61150</v>
+      </c>
+      <c r="F107" t="n">
+        <v>38845</v>
+      </c>
+      <c r="G107" t="n">
+        <v>63.52</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>395.4</v>
+        <v>2482.2</v>
       </c>
       <c r="C108" t="n">
-        <v>1549018</v>
+        <v>2482.2</v>
       </c>
       <c r="D108" t="n">
-        <v>559735</v>
+        <v>2482.2</v>
       </c>
       <c r="E108" t="n">
-        <v>36.13</v>
+        <v>100647</v>
+      </c>
+      <c r="F108" t="n">
+        <v>59827</v>
+      </c>
+      <c r="G108" t="n">
+        <v>59.44</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>396.3</v>
+        <v>2415.5</v>
       </c>
       <c r="C109" t="n">
-        <v>986293</v>
+        <v>2415.5</v>
       </c>
       <c r="D109" t="n">
-        <v>428843</v>
+        <v>2415.5</v>
       </c>
       <c r="E109" t="n">
-        <v>43.48</v>
+        <v>69127</v>
+      </c>
+      <c r="F109" t="n">
+        <v>33506</v>
+      </c>
+      <c r="G109" t="n">
+        <v>48.47</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>402.7</v>
+        <v>2409.2</v>
       </c>
       <c r="C110" t="n">
-        <v>898114</v>
+        <v>2409.2</v>
       </c>
       <c r="D110" t="n">
-        <v>352229</v>
+        <v>2409.2</v>
       </c>
       <c r="E110" t="n">
-        <v>39.22</v>
+        <v>37271</v>
+      </c>
+      <c r="F110" t="n">
+        <v>17643</v>
+      </c>
+      <c r="G110" t="n">
+        <v>47.34</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>388.2</v>
+        <v>2495.4</v>
       </c>
       <c r="C111" t="n">
-        <v>1408128</v>
+        <v>2495.4</v>
       </c>
       <c r="D111" t="n">
-        <v>669818</v>
+        <v>2495.4</v>
       </c>
       <c r="E111" t="n">
-        <v>47.57</v>
+        <v>71184</v>
+      </c>
+      <c r="F111" t="n">
+        <v>34859</v>
+      </c>
+      <c r="G111" t="n">
+        <v>48.97</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>382</v>
+        <v>2370.7</v>
       </c>
       <c r="C112" t="n">
-        <v>1728129</v>
+        <v>2370.7</v>
       </c>
       <c r="D112" t="n">
-        <v>837998</v>
+        <v>2370.7</v>
       </c>
       <c r="E112" t="n">
-        <v>48.49</v>
+        <v>13392</v>
+      </c>
+      <c r="F112" t="n">
+        <v>13392</v>
+      </c>
+      <c r="G112" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>381.7</v>
+        <v>2252.2</v>
       </c>
       <c r="C113" t="n">
-        <v>1092285</v>
+        <v>2252.2</v>
       </c>
       <c r="D113" t="n">
-        <v>510747</v>
+        <v>2252.2</v>
       </c>
       <c r="E113" t="n">
-        <v>46.76</v>
+        <v>10058</v>
+      </c>
+      <c r="F113" t="n">
+        <v>10058</v>
+      </c>
+      <c r="G113" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>371.3</v>
+        <v>2139.6</v>
       </c>
       <c r="C114" t="n">
-        <v>688160</v>
+        <v>2139.6</v>
       </c>
       <c r="D114" t="n">
-        <v>359554</v>
+        <v>2139.6</v>
       </c>
       <c r="E114" t="n">
-        <v>52.25</v>
+        <v>10612</v>
+      </c>
+      <c r="F114" t="n">
+        <v>10612</v>
+      </c>
+      <c r="G114" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>378.8</v>
+        <v>2032.7</v>
       </c>
       <c r="C115" t="n">
-        <v>1701866</v>
+        <v>2032.7</v>
       </c>
       <c r="D115" t="n">
-        <v>652268</v>
+        <v>2032.7</v>
       </c>
       <c r="E115" t="n">
-        <v>38.33</v>
+        <v>164243</v>
+      </c>
+      <c r="F115" t="n">
+        <v>111749</v>
+      </c>
+      <c r="G115" t="n">
+        <v>68.04000000000001</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>397.7</v>
+        <v>2134.3</v>
       </c>
       <c r="C116" t="n">
-        <v>1393285</v>
+        <v>2134.3</v>
       </c>
       <c r="D116" t="n">
-        <v>714129</v>
+        <v>2134.3</v>
       </c>
       <c r="E116" t="n">
-        <v>51.26</v>
+        <v>326923</v>
+      </c>
+      <c r="F116" t="n">
+        <v>148271</v>
+      </c>
+      <c r="G116" t="n">
+        <v>45.35</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>397.9</v>
+        <v>2103.5</v>
       </c>
       <c r="C117" t="n">
-        <v>1071224</v>
+        <v>2103.5</v>
       </c>
       <c r="D117" t="n">
-        <v>489874</v>
+        <v>2103.5</v>
       </c>
       <c r="E117" t="n">
-        <v>45.73</v>
+        <v>79576</v>
+      </c>
+      <c r="F117" t="n">
+        <v>44926</v>
+      </c>
+      <c r="G117" t="n">
+        <v>56.46</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>386.95</v>
+        <v>2079</v>
       </c>
       <c r="C118" t="n">
-        <v>751831</v>
+        <v>2079</v>
       </c>
       <c r="D118" t="n">
-        <v>399478</v>
+        <v>2079</v>
       </c>
       <c r="E118" t="n">
-        <v>53.13</v>
+        <v>78777</v>
+      </c>
+      <c r="F118" t="n">
+        <v>35954</v>
+      </c>
+      <c r="G118" t="n">
+        <v>45.64</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>394.6</v>
+        <v>2065.8</v>
       </c>
       <c r="C119" t="n">
-        <v>1171985</v>
+        <v>2065.8</v>
       </c>
       <c r="D119" t="n">
-        <v>501277</v>
+        <v>2065.8</v>
       </c>
       <c r="E119" t="n">
-        <v>42.77</v>
+        <v>43465</v>
+      </c>
+      <c r="F119" t="n">
+        <v>20376</v>
+      </c>
+      <c r="G119" t="n">
+        <v>46.88</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>410.9</v>
+        <v>2168.7</v>
       </c>
       <c r="C120" t="n">
-        <v>2148139</v>
+        <v>2168.7</v>
       </c>
       <c r="D120" t="n">
-        <v>937659</v>
+        <v>2168.7</v>
       </c>
       <c r="E120" t="n">
-        <v>43.65</v>
+        <v>67851</v>
+      </c>
+      <c r="F120" t="n">
+        <v>45069</v>
+      </c>
+      <c r="G120" t="n">
+        <v>66.42</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>423.5</v>
+        <v>2137.1</v>
       </c>
       <c r="C121" t="n">
-        <v>1838322</v>
+        <v>2137.1</v>
       </c>
       <c r="D121" t="n">
-        <v>823025</v>
+        <v>2137.1</v>
       </c>
       <c r="E121" t="n">
-        <v>44.77</v>
+        <v>37422</v>
+      </c>
+      <c r="F121" t="n">
+        <v>21466</v>
+      </c>
+      <c r="G121" t="n">
+        <v>57.36</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>404.95</v>
+        <v>2074.6</v>
       </c>
       <c r="C122" t="n">
-        <v>2414292</v>
+        <v>2074.6</v>
       </c>
       <c r="D122" t="n">
-        <v>1083588</v>
+        <v>2074.6</v>
       </c>
       <c r="E122" t="n">
-        <v>44.88</v>
+        <v>40365</v>
+      </c>
+      <c r="F122" t="n">
+        <v>21986</v>
+      </c>
+      <c r="G122" t="n">
+        <v>54.47</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>425.15</v>
+        <v>2085</v>
       </c>
       <c r="C123" t="n">
-        <v>2515611</v>
+        <v>2085</v>
       </c>
       <c r="D123" t="n">
-        <v>1389393</v>
+        <v>2085</v>
       </c>
       <c r="E123" t="n">
-        <v>55.23</v>
+        <v>52214</v>
+      </c>
+      <c r="F123" t="n">
+        <v>27246</v>
+      </c>
+      <c r="G123" t="n">
+        <v>52.18</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>446.4</v>
+        <v>2027</v>
       </c>
       <c r="C124" t="n">
-        <v>2758582</v>
+        <v>2027</v>
       </c>
       <c r="D124" t="n">
-        <v>1266059</v>
+        <v>2027</v>
       </c>
       <c r="E124" t="n">
-        <v>45.9</v>
+        <v>26806</v>
+      </c>
+      <c r="F124" t="n">
+        <v>14348</v>
+      </c>
+      <c r="G124" t="n">
+        <v>53.53</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>468.7</v>
+        <v>2029.1</v>
       </c>
       <c r="C125" t="n">
-        <v>121637</v>
+        <v>2029.1</v>
       </c>
       <c r="D125" t="n">
-        <v>121636</v>
+        <v>2029.1</v>
       </c>
       <c r="E125" t="n">
-        <v>100</v>
+        <v>33704</v>
+      </c>
+      <c r="F125" t="n">
+        <v>15238</v>
+      </c>
+      <c r="G125" t="n">
+        <v>45.21</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>492.1</v>
+        <v>2074.3</v>
       </c>
       <c r="C126" t="n">
-        <v>114305</v>
+        <v>2074.3</v>
       </c>
       <c r="D126" t="n">
-        <v>114305</v>
+        <v>2074.3</v>
       </c>
       <c r="E126" t="n">
-        <v>100</v>
+        <v>34481</v>
+      </c>
+      <c r="F126" t="n">
+        <v>18313</v>
+      </c>
+      <c r="G126" t="n">
+        <v>53.11</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>516.7</v>
+        <v>2080.8</v>
       </c>
       <c r="C127" t="n">
-        <v>7140040</v>
+        <v>2080.8</v>
       </c>
       <c r="D127" t="n">
-        <v>2730593</v>
+        <v>2080.8</v>
       </c>
       <c r="E127" t="n">
-        <v>38.24</v>
+        <v>28506</v>
+      </c>
+      <c r="F127" t="n">
+        <v>18022</v>
+      </c>
+      <c r="G127" t="n">
+        <v>63.22</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>542.5</v>
+        <v>2063.6</v>
       </c>
       <c r="C128" t="n">
-        <v>429556</v>
+        <v>2063.6</v>
       </c>
       <c r="D128" t="n">
-        <v>359916</v>
+        <v>2063.6</v>
       </c>
       <c r="E128" t="n">
-        <v>83.79000000000001</v>
+        <v>30693</v>
+      </c>
+      <c r="F128" t="n">
+        <v>17881</v>
+      </c>
+      <c r="G128" t="n">
+        <v>58.26</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>515.4</v>
+        <v>2104</v>
       </c>
       <c r="C129" t="n">
-        <v>5885813</v>
+        <v>2104</v>
       </c>
       <c r="D129" t="n">
-        <v>2431429</v>
+        <v>2104</v>
       </c>
       <c r="E129" t="n">
-        <v>41.31</v>
+        <v>38436</v>
+      </c>
+      <c r="F129" t="n">
+        <v>18954</v>
+      </c>
+      <c r="G129" t="n">
+        <v>49.31</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>491.45</v>
+        <v>2160</v>
       </c>
       <c r="C130" t="n">
-        <v>5202149</v>
+        <v>2160</v>
       </c>
       <c r="D130" t="n">
-        <v>1793275</v>
+        <v>2160</v>
       </c>
       <c r="E130" t="n">
-        <v>34.47</v>
+        <v>37923</v>
+      </c>
+      <c r="F130" t="n">
+        <v>19528</v>
+      </c>
+      <c r="G130" t="n">
+        <v>51.49</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>492.55</v>
+        <v>2305.7</v>
       </c>
       <c r="C131" t="n">
-        <v>1788213</v>
+        <v>2305.7</v>
       </c>
       <c r="D131" t="n">
-        <v>698634</v>
+        <v>2305.7</v>
       </c>
       <c r="E131" t="n">
-        <v>39.07</v>
+        <v>85579</v>
+      </c>
+      <c r="F131" t="n">
+        <v>40423</v>
+      </c>
+      <c r="G131" t="n">
+        <v>47.23</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>517.15</v>
+        <v>2331.1</v>
       </c>
       <c r="C132" t="n">
-        <v>217316</v>
+        <v>2331.1</v>
       </c>
       <c r="D132" t="n">
-        <v>212691</v>
+        <v>2331.1</v>
       </c>
       <c r="E132" t="n">
-        <v>97.87</v>
+        <v>75163</v>
+      </c>
+      <c r="F132" t="n">
+        <v>39044</v>
+      </c>
+      <c r="G132" t="n">
+        <v>51.95</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>543</v>
+        <v>2343.8</v>
       </c>
       <c r="C133" t="n">
-        <v>539520</v>
+        <v>2343.8</v>
       </c>
       <c r="D133" t="n">
-        <v>356236</v>
+        <v>2343.8</v>
       </c>
       <c r="E133" t="n">
-        <v>66.03</v>
+        <v>39861</v>
+      </c>
+      <c r="F133" t="n">
+        <v>20317</v>
+      </c>
+      <c r="G133" t="n">
+        <v>50.97</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>570.15</v>
+        <v>2362.6</v>
       </c>
       <c r="C134" t="n">
-        <v>2968119</v>
+        <v>2362.6</v>
       </c>
       <c r="D134" t="n">
-        <v>1241421</v>
+        <v>2362.6</v>
       </c>
       <c r="E134" t="n">
-        <v>41.83</v>
+        <v>41431</v>
+      </c>
+      <c r="F134" t="n">
+        <v>21350</v>
+      </c>
+      <c r="G134" t="n">
+        <v>51.53</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>598.65</v>
+        <v>2360.6</v>
       </c>
       <c r="C135" t="n">
-        <v>2619172</v>
+        <v>2360.6</v>
       </c>
       <c r="D135" t="n">
-        <v>1002999</v>
+        <v>2360.6</v>
       </c>
       <c r="E135" t="n">
-        <v>38.29</v>
+        <v>46951</v>
+      </c>
+      <c r="F135" t="n">
+        <v>23349</v>
+      </c>
+      <c r="G135" t="n">
+        <v>49.73</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>605.7</v>
+        <v>2352.8</v>
       </c>
       <c r="C136" t="n">
-        <v>3029968</v>
+        <v>2352.8</v>
       </c>
       <c r="D136" t="n">
-        <v>1078350</v>
+        <v>2352.8</v>
       </c>
       <c r="E136" t="n">
-        <v>35.59</v>
+        <v>108389</v>
+      </c>
+      <c r="F136" t="n">
+        <v>52697</v>
+      </c>
+      <c r="G136" t="n">
+        <v>48.62</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>575.45</v>
+        <v>2295.1</v>
       </c>
       <c r="C137" t="n">
-        <v>2106565</v>
+        <v>2295.1</v>
       </c>
       <c r="D137" t="n">
-        <v>1042804</v>
+        <v>2295.1</v>
       </c>
       <c r="E137" t="n">
-        <v>49.5</v>
+        <v>59806</v>
+      </c>
+      <c r="F137" t="n">
+        <v>39300</v>
+      </c>
+      <c r="G137" t="n">
+        <v>65.70999999999999</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>2270</v>
+      </c>
+      <c r="C138" t="n">
+        <v>2270</v>
+      </c>
+      <c r="D138" t="n">
+        <v>2270</v>
+      </c>
+      <c r="E138" t="n">
+        <v>60811</v>
+      </c>
+      <c r="F138" t="n">
+        <v>32809</v>
+      </c>
+      <c r="G138" t="n">
+        <v>53.95</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>2403.1</v>
+      </c>
+      <c r="C139" t="n">
+        <v>2403.1</v>
+      </c>
+      <c r="D139" t="n">
+        <v>2403.1</v>
+      </c>
+      <c r="E139" t="n">
+        <v>93427</v>
+      </c>
+      <c r="F139" t="n">
+        <v>45360</v>
+      </c>
+      <c r="G139" t="n">
+        <v>48.55</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>2643.4</v>
+      </c>
+      <c r="C140" t="n">
+        <v>2643.4</v>
+      </c>
+      <c r="D140" t="n">
+        <v>2643.4</v>
+      </c>
+      <c r="E140" t="n">
+        <v>303681</v>
+      </c>
+      <c r="F140" t="n">
+        <v>104198</v>
+      </c>
+      <c r="G140" t="n">
+        <v>34.31</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>2867.7</v>
+      </c>
+      <c r="C141" t="n">
+        <v>2867.7</v>
+      </c>
+      <c r="D141" t="n">
+        <v>2867.7</v>
+      </c>
+      <c r="E141" t="n">
+        <v>438965</v>
+      </c>
+      <c r="F141" t="n">
+        <v>152883</v>
+      </c>
+      <c r="G141" t="n">
+        <v>34.83</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>2900</v>
+      </c>
+      <c r="C142" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D142" t="n">
+        <v>2900</v>
+      </c>
+      <c r="E142" t="n">
+        <v>201614</v>
+      </c>
+      <c r="F142" t="n">
+        <v>69921</v>
+      </c>
+      <c r="G142" t="n">
+        <v>34.68</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>2961.6</v>
+      </c>
+      <c r="C143" t="n">
+        <v>2961.6</v>
+      </c>
+      <c r="D143" t="n">
+        <v>2961.6</v>
+      </c>
+      <c r="E143" t="n">
+        <v>85073</v>
+      </c>
+      <c r="F143" t="n">
+        <v>40832</v>
+      </c>
+      <c r="G143" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>3109.6</v>
+      </c>
+      <c r="C144" t="n">
+        <v>3109.6</v>
+      </c>
+      <c r="D144" t="n">
+        <v>3109.6</v>
+      </c>
+      <c r="E144" t="n">
+        <v>177169</v>
+      </c>
+      <c r="F144" t="n">
+        <v>80048</v>
+      </c>
+      <c r="G144" t="n">
+        <v>45.18</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>3265</v>
+      </c>
+      <c r="C145" t="n">
+        <v>3265</v>
+      </c>
+      <c r="D145" t="n">
+        <v>3265</v>
+      </c>
+      <c r="E145" t="n">
+        <v>125642</v>
+      </c>
+      <c r="F145" t="n">
+        <v>57813</v>
+      </c>
+      <c r="G145" t="n">
+        <v>46.01</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>3246.4</v>
+      </c>
+      <c r="C146" t="n">
+        <v>3246.4</v>
+      </c>
+      <c r="D146" t="n">
+        <v>3246.4</v>
+      </c>
+      <c r="E146" t="n">
+        <v>320583</v>
+      </c>
+      <c r="F146" t="n">
+        <v>107918</v>
+      </c>
+      <c r="G146" t="n">
+        <v>33.66</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>3084.1</v>
+      </c>
+      <c r="C147" t="n">
+        <v>3084.1</v>
+      </c>
+      <c r="D147" t="n">
+        <v>3084.1</v>
+      </c>
+      <c r="E147" t="n">
+        <v>104991</v>
+      </c>
+      <c r="F147" t="n">
+        <v>61933</v>
+      </c>
+      <c r="G147" t="n">
+        <v>58.99</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>3014.4</v>
+      </c>
+      <c r="C148" t="n">
+        <v>3014.4</v>
+      </c>
+      <c r="D148" t="n">
+        <v>3014.4</v>
+      </c>
+      <c r="E148" t="n">
+        <v>150056</v>
+      </c>
+      <c r="F148" t="n">
+        <v>77094</v>
+      </c>
+      <c r="G148" t="n">
+        <v>51.38</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>3016.5</v>
+      </c>
+      <c r="C149" t="n">
+        <v>3016.5</v>
+      </c>
+      <c r="D149" t="n">
+        <v>3016.5</v>
+      </c>
+      <c r="E149" t="n">
+        <v>58540</v>
+      </c>
+      <c r="F149" t="n">
+        <v>23719</v>
+      </c>
+      <c r="G149" t="n">
+        <v>40.52</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>2979.3</v>
+      </c>
+      <c r="C150" t="n">
+        <v>2979.3</v>
+      </c>
+      <c r="D150" t="n">
+        <v>2979.3</v>
+      </c>
+      <c r="E150" t="n">
+        <v>84424</v>
+      </c>
+      <c r="F150" t="n">
+        <v>33187</v>
+      </c>
+      <c r="G150" t="n">
+        <v>39.31</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>2956.4</v>
+      </c>
+      <c r="C151" t="n">
+        <v>2956.4</v>
+      </c>
+      <c r="D151" t="n">
+        <v>2956.4</v>
+      </c>
+      <c r="E151" t="n">
+        <v>55974</v>
+      </c>
+      <c r="F151" t="n">
+        <v>24622</v>
+      </c>
+      <c r="G151" t="n">
+        <v>43.99</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>3039.9</v>
+      </c>
+      <c r="C152" t="n">
+        <v>3039.9</v>
+      </c>
+      <c r="D152" t="n">
+        <v>3039.9</v>
+      </c>
+      <c r="E152" t="n">
+        <v>91080</v>
+      </c>
+      <c r="F152" t="n">
+        <v>38664</v>
+      </c>
+      <c r="G152" t="n">
+        <v>42.45</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>3191.8</v>
+      </c>
+      <c r="C153" t="n">
+        <v>3191.8</v>
+      </c>
+      <c r="D153" t="n">
+        <v>3191.8</v>
+      </c>
+      <c r="E153" t="n">
+        <v>57761</v>
+      </c>
+      <c r="F153" t="n">
+        <v>40605</v>
+      </c>
+      <c r="G153" t="n">
+        <v>70.3</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>3351.3</v>
+      </c>
+      <c r="C154" t="n">
+        <v>3351.3</v>
+      </c>
+      <c r="D154" t="n">
+        <v>3351.3</v>
+      </c>
+      <c r="E154" t="n">
+        <v>190016</v>
+      </c>
+      <c r="F154" t="n">
+        <v>81790</v>
+      </c>
+      <c r="G154" t="n">
+        <v>43.04</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>3218.6</v>
+      </c>
+      <c r="C155" t="n">
+        <v>3218.6</v>
+      </c>
+      <c r="D155" t="n">
+        <v>3218.6</v>
+      </c>
+      <c r="E155" t="n">
+        <v>221986</v>
+      </c>
+      <c r="F155" t="n">
+        <v>89950</v>
+      </c>
+      <c r="G155" t="n">
+        <v>40.52</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>3320.3</v>
+      </c>
+      <c r="C156" t="n">
+        <v>3320.3</v>
+      </c>
+      <c r="D156" t="n">
+        <v>3320.3</v>
+      </c>
+      <c r="E156" t="n">
+        <v>123230</v>
+      </c>
+      <c r="F156" t="n">
+        <v>45759</v>
+      </c>
+      <c r="G156" t="n">
+        <v>37.13</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>3450.8</v>
+      </c>
+      <c r="C157" t="n">
+        <v>3450.8</v>
+      </c>
+      <c r="D157" t="n">
+        <v>3450.8</v>
+      </c>
+      <c r="E157" t="n">
+        <v>276623</v>
+      </c>
+      <c r="F157" t="n">
+        <v>106241</v>
+      </c>
+      <c r="G157" t="n">
+        <v>38.41</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>3305.6</v>
+      </c>
+      <c r="C158" t="n">
+        <v>3305.6</v>
+      </c>
+      <c r="D158" t="n">
+        <v>3305.6</v>
+      </c>
+      <c r="E158" t="n">
+        <v>252587</v>
+      </c>
+      <c r="F158" t="n">
+        <v>85859</v>
+      </c>
+      <c r="G158" t="n">
+        <v>33.99</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>3204.3</v>
+      </c>
+      <c r="C159" t="n">
+        <v>3204.3</v>
+      </c>
+      <c r="D159" t="n">
+        <v>3204.3</v>
+      </c>
+      <c r="E159" t="n">
+        <v>116753</v>
+      </c>
+      <c r="F159" t="n">
+        <v>42871</v>
+      </c>
+      <c r="G159" t="n">
+        <v>36.72</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>3364.5</v>
+      </c>
+      <c r="C160" t="n">
+        <v>3364.5</v>
+      </c>
+      <c r="D160" t="n">
+        <v>3364.5</v>
+      </c>
+      <c r="E160" t="n">
+        <v>100433</v>
+      </c>
+      <c r="F160" t="n">
+        <v>47408</v>
+      </c>
+      <c r="G160" t="n">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>3532.7</v>
+      </c>
+      <c r="C161" t="n">
+        <v>3532.7</v>
+      </c>
+      <c r="D161" t="n">
+        <v>3532.7</v>
+      </c>
+      <c r="E161" t="n">
+        <v>98922</v>
+      </c>
+      <c r="F161" t="n">
+        <v>45120</v>
+      </c>
+      <c r="G161" t="n">
+        <v>45.61</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>3709.3</v>
+      </c>
+      <c r="C162" t="n">
+        <v>3709.3</v>
+      </c>
+      <c r="D162" t="n">
+        <v>3709.3</v>
+      </c>
+      <c r="E162" t="n">
+        <v>75231</v>
+      </c>
+      <c r="F162" t="n">
+        <v>43683</v>
+      </c>
+      <c r="G162" t="n">
+        <v>58.07</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>3743.5</v>
+      </c>
+      <c r="C163" t="n">
+        <v>3743.5</v>
+      </c>
+      <c r="D163" t="n">
+        <v>3743.5</v>
+      </c>
+      <c r="E163" t="n">
+        <v>344233</v>
+      </c>
+      <c r="F163" t="n">
+        <v>131499</v>
+      </c>
+      <c r="G163" t="n">
+        <v>38.2</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>3726.9</v>
+      </c>
+      <c r="C164" t="n">
+        <v>3726.9</v>
+      </c>
+      <c r="D164" t="n">
+        <v>3726.9</v>
+      </c>
+      <c r="E164" t="n">
+        <v>130039</v>
+      </c>
+      <c r="F164" t="n">
+        <v>49115</v>
+      </c>
+      <c r="G164" t="n">
+        <v>37.77</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>3465.6</v>
+      </c>
+      <c r="C165" t="n">
+        <v>3465.6</v>
+      </c>
+      <c r="D165" t="n">
+        <v>3465.6</v>
+      </c>
+      <c r="E165" t="n">
+        <v>219701</v>
+      </c>
+      <c r="F165" t="n">
+        <v>96634</v>
+      </c>
+      <c r="G165" t="n">
+        <v>43.98</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>3407.8</v>
+      </c>
+      <c r="C166" t="n">
+        <v>3407.8</v>
+      </c>
+      <c r="D166" t="n">
+        <v>3407.8</v>
+      </c>
+      <c r="E166" t="n">
+        <v>111052</v>
+      </c>
+      <c r="F166" t="n">
+        <v>39748</v>
+      </c>
+      <c r="G166" t="n">
+        <v>35.79</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>3300.4</v>
+      </c>
+      <c r="C167" t="n">
+        <v>3300.4</v>
+      </c>
+      <c r="D167" t="n">
+        <v>3300.4</v>
+      </c>
+      <c r="E167" t="n">
+        <v>163423</v>
+      </c>
+      <c r="F167" t="n">
+        <v>71816</v>
+      </c>
+      <c r="G167" t="n">
+        <v>43.94</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>3197.2</v>
+      </c>
+      <c r="C168" t="n">
+        <v>3197.2</v>
+      </c>
+      <c r="D168" t="n">
+        <v>3197.2</v>
+      </c>
+      <c r="E168" t="n">
+        <v>140930</v>
+      </c>
+      <c r="F168" t="n">
+        <v>55454</v>
+      </c>
+      <c r="G168" t="n">
+        <v>39.35</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>3201.7</v>
+      </c>
+      <c r="C169" t="n">
+        <v>3201.7</v>
+      </c>
+      <c r="D169" t="n">
+        <v>3201.7</v>
+      </c>
+      <c r="E169" t="n">
+        <v>129274</v>
+      </c>
+      <c r="F169" t="n">
+        <v>47160</v>
+      </c>
+      <c r="G169" t="n">
+        <v>36.48</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>3209.5</v>
+      </c>
+      <c r="C170" t="n">
+        <v>3209.5</v>
+      </c>
+      <c r="D170" t="n">
+        <v>3209.5</v>
+      </c>
+      <c r="E170" t="n">
+        <v>106163</v>
+      </c>
+      <c r="F170" t="n">
+        <v>45613</v>
+      </c>
+      <c r="G170" t="n">
+        <v>42.97</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>3241.3</v>
+      </c>
+      <c r="C171" t="n">
+        <v>3241.3</v>
+      </c>
+      <c r="D171" t="n">
+        <v>3241.3</v>
+      </c>
+      <c r="E171" t="n">
+        <v>152721</v>
+      </c>
+      <c r="F171" t="n">
+        <v>65797</v>
+      </c>
+      <c r="G171" t="n">
+        <v>43.08</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>3181</v>
+      </c>
+      <c r="C172" t="n">
+        <v>3181</v>
+      </c>
+      <c r="D172" t="n">
+        <v>3181</v>
+      </c>
+      <c r="E172" t="n">
+        <v>67056</v>
+      </c>
+      <c r="F172" t="n">
+        <v>26938</v>
+      </c>
+      <c r="G172" t="n">
+        <v>40.17</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>3198.7</v>
+      </c>
+      <c r="C173" t="n">
+        <v>3198.7</v>
+      </c>
+      <c r="D173" t="n">
+        <v>3198.7</v>
+      </c>
+      <c r="E173" t="n">
+        <v>14283</v>
+      </c>
+      <c r="F173" t="n">
+        <v>6953</v>
+      </c>
+      <c r="G173" t="n">
+        <v>48.68</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>3207.4</v>
+      </c>
+      <c r="C174" t="n">
+        <v>3207.4</v>
+      </c>
+      <c r="D174" t="n">
+        <v>3207.4</v>
+      </c>
+      <c r="E174" t="n">
+        <v>79088</v>
+      </c>
+      <c r="F174" t="n">
+        <v>42629</v>
+      </c>
+      <c r="G174" t="n">
+        <v>53.9</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>3068.2</v>
+      </c>
+      <c r="C175" t="n">
+        <v>3068.2</v>
+      </c>
+      <c r="D175" t="n">
+        <v>3068.2</v>
+      </c>
+      <c r="E175" t="n">
+        <v>74004</v>
+      </c>
+      <c r="F175" t="n">
+        <v>38356</v>
+      </c>
+      <c r="G175" t="n">
+        <v>51.83</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>3175.8</v>
+      </c>
+      <c r="C176" t="n">
+        <v>3175.8</v>
+      </c>
+      <c r="D176" t="n">
+        <v>3175.8</v>
+      </c>
+      <c r="E176" t="n">
+        <v>174963</v>
+      </c>
+      <c r="F176" t="n">
+        <v>75086</v>
+      </c>
+      <c r="G176" t="n">
+        <v>42.92</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>3119.3</v>
+      </c>
+      <c r="C177" t="n">
+        <v>3119.3</v>
+      </c>
+      <c r="D177" t="n">
+        <v>3119.3</v>
+      </c>
+      <c r="E177" t="n">
+        <v>65002</v>
+      </c>
+      <c r="F177" t="n">
+        <v>35226</v>
+      </c>
+      <c r="G177" t="n">
+        <v>54.19</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>3090.8</v>
+      </c>
+      <c r="C178" t="n">
+        <v>3090.8</v>
+      </c>
+      <c r="D178" t="n">
+        <v>3090.8</v>
+      </c>
+      <c r="E178" t="n">
+        <v>49590</v>
+      </c>
+      <c r="F178" t="n">
+        <v>22956</v>
+      </c>
+      <c r="G178" t="n">
+        <v>46.29</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>3117.9</v>
+      </c>
+      <c r="C179" t="n">
+        <v>3117.9</v>
+      </c>
+      <c r="D179" t="n">
+        <v>3117.9</v>
+      </c>
+      <c r="E179" t="n">
+        <v>43842</v>
+      </c>
+      <c r="F179" t="n">
+        <v>18927</v>
+      </c>
+      <c r="G179" t="n">
+        <v>43.17</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>3092.6</v>
+      </c>
+      <c r="C180" t="n">
+        <v>3092.6</v>
+      </c>
+      <c r="D180" t="n">
+        <v>3092.6</v>
+      </c>
+      <c r="E180" t="n">
+        <v>38734</v>
+      </c>
+      <c r="F180" t="n">
+        <v>16430</v>
+      </c>
+      <c r="G180" t="n">
+        <v>42.42</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>3048.3</v>
+      </c>
+      <c r="C181" t="n">
+        <v>3048.3</v>
+      </c>
+      <c r="D181" t="n">
+        <v>3048.3</v>
+      </c>
+      <c r="E181" t="n">
+        <v>39410</v>
+      </c>
+      <c r="F181" t="n">
+        <v>19763</v>
+      </c>
+      <c r="G181" t="n">
+        <v>50.15</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>3113.3</v>
+      </c>
+      <c r="C182" t="n">
+        <v>3113.3</v>
+      </c>
+      <c r="D182" t="n">
+        <v>3113.3</v>
+      </c>
+      <c r="E182" t="n">
+        <v>55655</v>
+      </c>
+      <c r="F182" t="n">
+        <v>28457</v>
+      </c>
+      <c r="G182" t="n">
+        <v>51.13</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>3047.9</v>
+      </c>
+      <c r="C183" t="n">
+        <v>3047.9</v>
+      </c>
+      <c r="D183" t="n">
+        <v>3047.9</v>
+      </c>
+      <c r="E183" t="n">
+        <v>101280</v>
+      </c>
+      <c r="F183" t="n">
+        <v>49288</v>
+      </c>
+      <c r="G183" t="n">
+        <v>48.67</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>3077.2</v>
+      </c>
+      <c r="C184" t="n">
+        <v>3077.2</v>
+      </c>
+      <c r="D184" t="n">
+        <v>3077.2</v>
+      </c>
+      <c r="E184" t="n">
+        <v>92269</v>
+      </c>
+      <c r="F184" t="n">
+        <v>38877</v>
+      </c>
+      <c r="G184" t="n">
+        <v>42.13</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>3048.7</v>
+      </c>
+      <c r="C185" t="n">
+        <v>3048.7</v>
+      </c>
+      <c r="D185" t="n">
+        <v>3048.7</v>
+      </c>
+      <c r="E185" t="n">
+        <v>72690</v>
+      </c>
+      <c r="F185" t="n">
+        <v>37568</v>
+      </c>
+      <c r="G185" t="n">
+        <v>51.68</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>2924.6</v>
+      </c>
+      <c r="C186" t="n">
+        <v>2924.6</v>
+      </c>
+      <c r="D186" t="n">
+        <v>2924.6</v>
+      </c>
+      <c r="E186" t="n">
+        <v>276383</v>
+      </c>
+      <c r="F186" t="n">
+        <v>97725</v>
+      </c>
+      <c r="G186" t="n">
+        <v>35.36</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>2915.5</v>
+      </c>
+      <c r="C187" t="n">
+        <v>2915.5</v>
+      </c>
+      <c r="D187" t="n">
+        <v>2915.5</v>
+      </c>
+      <c r="E187" t="n">
+        <v>330298</v>
+      </c>
+      <c r="F187" t="n">
+        <v>140770</v>
+      </c>
+      <c r="G187" t="n">
+        <v>42.62</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>2812.1</v>
+      </c>
+      <c r="C188" t="n">
+        <v>2812.1</v>
+      </c>
+      <c r="D188" t="n">
+        <v>2812.1</v>
+      </c>
+      <c r="E188" t="n">
+        <v>81797</v>
+      </c>
+      <c r="F188" t="n">
+        <v>35048</v>
+      </c>
+      <c r="G188" t="n">
+        <v>42.85</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>2647.1</v>
+      </c>
+      <c r="C189" t="n">
+        <v>2647.1</v>
+      </c>
+      <c r="D189" t="n">
+        <v>2647.1</v>
+      </c>
+      <c r="E189" t="n">
+        <v>156734</v>
+      </c>
+      <c r="F189" t="n">
+        <v>100535</v>
+      </c>
+      <c r="G189" t="n">
+        <v>64.14</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>2611.6</v>
+      </c>
+      <c r="C190" t="n">
+        <v>2611.6</v>
+      </c>
+      <c r="D190" t="n">
+        <v>2611.6</v>
+      </c>
+      <c r="E190" t="n">
+        <v>135780</v>
+      </c>
+      <c r="F190" t="n">
+        <v>62952</v>
+      </c>
+      <c r="G190" t="n">
+        <v>46.36</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>2588.9</v>
+      </c>
+      <c r="C191" t="n">
+        <v>2588.9</v>
+      </c>
+      <c r="D191" t="n">
+        <v>2588.9</v>
+      </c>
+      <c r="E191" t="n">
+        <v>137808</v>
+      </c>
+      <c r="F191" t="n">
+        <v>54051</v>
+      </c>
+      <c r="G191" t="n">
+        <v>39.22</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>2603.6</v>
+      </c>
+      <c r="C192" t="n">
+        <v>2603.6</v>
+      </c>
+      <c r="D192" t="n">
+        <v>2603.6</v>
+      </c>
+      <c r="E192" t="n">
+        <v>73560</v>
+      </c>
+      <c r="F192" t="n">
+        <v>33595</v>
+      </c>
+      <c r="G192" t="n">
+        <v>45.67</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>2585.7</v>
+      </c>
+      <c r="C193" t="n">
+        <v>2585.7</v>
+      </c>
+      <c r="D193" t="n">
+        <v>2585.7</v>
+      </c>
+      <c r="E193" t="n">
+        <v>78341</v>
+      </c>
+      <c r="F193" t="n">
+        <v>31427</v>
+      </c>
+      <c r="G193" t="n">
+        <v>40.12</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>2479.2</v>
+      </c>
+      <c r="C194" t="n">
+        <v>2479.2</v>
+      </c>
+      <c r="D194" t="n">
+        <v>2479.2</v>
+      </c>
+      <c r="E194" t="n">
+        <v>59011</v>
+      </c>
+      <c r="F194" t="n">
+        <v>29062</v>
+      </c>
+      <c r="G194" t="n">
+        <v>49.25</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>2328.4</v>
+      </c>
+      <c r="C195" t="n">
+        <v>2328.4</v>
+      </c>
+      <c r="D195" t="n">
+        <v>2328.4</v>
+      </c>
+      <c r="E195" t="n">
+        <v>115582</v>
+      </c>
+      <c r="F195" t="n">
+        <v>59910</v>
+      </c>
+      <c r="G195" t="n">
+        <v>51.83</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>2325.8</v>
+      </c>
+      <c r="C196" t="n">
+        <v>2325.8</v>
+      </c>
+      <c r="D196" t="n">
+        <v>2325.8</v>
+      </c>
+      <c r="E196" t="n">
+        <v>103188</v>
+      </c>
+      <c r="F196" t="n">
+        <v>39607</v>
+      </c>
+      <c r="G196" t="n">
+        <v>38.38</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>2345.7</v>
+      </c>
+      <c r="C197" t="n">
+        <v>2345.7</v>
+      </c>
+      <c r="D197" t="n">
+        <v>2345.7</v>
+      </c>
+      <c r="E197" t="n">
+        <v>76864</v>
+      </c>
+      <c r="F197" t="n">
+        <v>24656</v>
+      </c>
+      <c r="G197" t="n">
+        <v>32.08</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>2310.2</v>
+      </c>
+      <c r="C198" t="n">
+        <v>2310.2</v>
+      </c>
+      <c r="D198" t="n">
+        <v>2310.2</v>
+      </c>
+      <c r="E198" t="n">
+        <v>60856</v>
+      </c>
+      <c r="F198" t="n">
+        <v>27273</v>
+      </c>
+      <c r="G198" t="n">
+        <v>44.82</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>2261.8</v>
+      </c>
+      <c r="C199" t="n">
+        <v>2261.8</v>
+      </c>
+      <c r="D199" t="n">
+        <v>2261.8</v>
+      </c>
+      <c r="E199" t="n">
+        <v>70341</v>
+      </c>
+      <c r="F199" t="n">
+        <v>38709</v>
+      </c>
+      <c r="G199" t="n">
+        <v>55.03</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>2290.1</v>
+      </c>
+      <c r="C200" t="n">
+        <v>2290.1</v>
+      </c>
+      <c r="D200" t="n">
+        <v>2290.1</v>
+      </c>
+      <c r="E200" t="n">
+        <v>83064</v>
+      </c>
+      <c r="F200" t="n">
+        <v>29690</v>
+      </c>
+      <c r="G200" t="n">
+        <v>35.74</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>2203.8</v>
+      </c>
+      <c r="C201" t="n">
+        <v>2203.8</v>
+      </c>
+      <c r="D201" t="n">
+        <v>2203.8</v>
+      </c>
+      <c r="E201" t="n">
+        <v>62835</v>
+      </c>
+      <c r="F201" t="n">
+        <v>34058</v>
+      </c>
+      <c r="G201" t="n">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>2142.4</v>
+      </c>
+      <c r="C202" t="n">
+        <v>2142.4</v>
+      </c>
+      <c r="D202" t="n">
+        <v>2142.4</v>
+      </c>
+      <c r="E202" t="n">
+        <v>141444</v>
+      </c>
+      <c r="F202" t="n">
+        <v>84801</v>
+      </c>
+      <c r="G202" t="n">
+        <v>59.95</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>2204.6</v>
+      </c>
+      <c r="C203" t="n">
+        <v>2204.6</v>
+      </c>
+      <c r="D203" t="n">
+        <v>2204.6</v>
+      </c>
+      <c r="E203" t="n">
+        <v>150458</v>
+      </c>
+      <c r="F203" t="n">
+        <v>56410</v>
+      </c>
+      <c r="G203" t="n">
+        <v>37.49</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>2123.8</v>
+      </c>
+      <c r="C204" t="n">
+        <v>2123.8</v>
+      </c>
+      <c r="D204" t="n">
+        <v>2123.8</v>
+      </c>
+      <c r="E204" t="n">
+        <v>162517</v>
+      </c>
+      <c r="F204" t="n">
+        <v>71086</v>
+      </c>
+      <c r="G204" t="n">
+        <v>43.74</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C205" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D205" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E205" t="n">
+        <v>121978</v>
+      </c>
+      <c r="F205" t="n">
+        <v>61965</v>
+      </c>
+      <c r="G205" t="n">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>2150.1</v>
+      </c>
+      <c r="C206" t="n">
+        <v>2150.1</v>
+      </c>
+      <c r="D206" t="n">
+        <v>2150.1</v>
+      </c>
+      <c r="E206" t="n">
+        <v>182116</v>
+      </c>
+      <c r="F206" t="n">
+        <v>59666</v>
+      </c>
+      <c r="G206" t="n">
+        <v>32.76</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>2085.4</v>
+      </c>
+      <c r="C207" t="n">
+        <v>2085.4</v>
+      </c>
+      <c r="D207" t="n">
+        <v>2085.4</v>
+      </c>
+      <c r="E207" t="n">
+        <v>133417</v>
+      </c>
+      <c r="F207" t="n">
+        <v>54403</v>
+      </c>
+      <c r="G207" t="n">
+        <v>40.78</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>2105.9</v>
+      </c>
+      <c r="C208" t="n">
+        <v>2105.9</v>
+      </c>
+      <c r="D208" t="n">
+        <v>2105.9</v>
+      </c>
+      <c r="E208" t="n">
+        <v>74577</v>
+      </c>
+      <c r="F208" t="n">
+        <v>29039</v>
+      </c>
+      <c r="G208" t="n">
+        <v>38.94</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>2104.8</v>
+      </c>
+      <c r="C209" t="n">
+        <v>2104.8</v>
+      </c>
+      <c r="D209" t="n">
+        <v>2104.8</v>
+      </c>
+      <c r="E209" t="n">
+        <v>84593</v>
+      </c>
+      <c r="F209" t="n">
+        <v>36017</v>
+      </c>
+      <c r="G209" t="n">
+        <v>42.58</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>2102.6</v>
+      </c>
+      <c r="C210" t="n">
+        <v>2102.6</v>
+      </c>
+      <c r="D210" t="n">
+        <v>2102.6</v>
+      </c>
+      <c r="E210" t="n">
+        <v>74138</v>
+      </c>
+      <c r="F210" t="n">
+        <v>33190</v>
+      </c>
+      <c r="G210" t="n">
+        <v>44.77</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>2039.6</v>
+      </c>
+      <c r="C211" t="n">
+        <v>2039.6</v>
+      </c>
+      <c r="D211" t="n">
+        <v>2039.6</v>
+      </c>
+      <c r="E211" t="n">
+        <v>71650</v>
+      </c>
+      <c r="F211" t="n">
+        <v>42324</v>
+      </c>
+      <c r="G211" t="n">
+        <v>59.07</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>2013.8</v>
+      </c>
+      <c r="C212" t="n">
+        <v>2013.8</v>
+      </c>
+      <c r="D212" t="n">
+        <v>2013.8</v>
+      </c>
+      <c r="E212" t="n">
+        <v>40512</v>
+      </c>
+      <c r="F212" t="n">
+        <v>20631</v>
+      </c>
+      <c r="G212" t="n">
+        <v>50.93</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>2009.9</v>
+      </c>
+      <c r="C213" t="n">
+        <v>2009.9</v>
+      </c>
+      <c r="D213" t="n">
+        <v>2009.9</v>
+      </c>
+      <c r="E213" t="n">
+        <v>49447</v>
+      </c>
+      <c r="F213" t="n">
+        <v>20334</v>
+      </c>
+      <c r="G213" t="n">
+        <v>41.12</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>2063.2</v>
+      </c>
+      <c r="C214" t="n">
+        <v>2063.2</v>
+      </c>
+      <c r="D214" t="n">
+        <v>2063.2</v>
+      </c>
+      <c r="E214" t="n">
+        <v>78269</v>
+      </c>
+      <c r="F214" t="n">
+        <v>31826</v>
+      </c>
+      <c r="G214" t="n">
+        <v>40.66</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>2079.7</v>
+      </c>
+      <c r="C215" t="n">
+        <v>2079.7</v>
+      </c>
+      <c r="D215" t="n">
+        <v>2079.7</v>
+      </c>
+      <c r="E215" t="n">
+        <v>82802</v>
+      </c>
+      <c r="F215" t="n">
+        <v>36430</v>
+      </c>
+      <c r="G215" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>2095.3</v>
+      </c>
+      <c r="C216" t="n">
+        <v>2095.3</v>
+      </c>
+      <c r="D216" t="n">
+        <v>2095.3</v>
+      </c>
+      <c r="E216" t="n">
+        <v>45047</v>
+      </c>
+      <c r="F216" t="n">
+        <v>20460</v>
+      </c>
+      <c r="G216" t="n">
+        <v>45.42</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>2079.4</v>
+      </c>
+      <c r="C217" t="n">
+        <v>2079.4</v>
+      </c>
+      <c r="D217" t="n">
+        <v>2079.4</v>
+      </c>
+      <c r="E217" t="n">
+        <v>31746</v>
+      </c>
+      <c r="F217" t="n">
+        <v>14611</v>
+      </c>
+      <c r="G217" t="n">
+        <v>46.02</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>2050.8</v>
+      </c>
+      <c r="C218" t="n">
+        <v>2050.8</v>
+      </c>
+      <c r="D218" t="n">
+        <v>2050.8</v>
+      </c>
+      <c r="E218" t="n">
+        <v>31159</v>
+      </c>
+      <c r="F218" t="n">
+        <v>17404</v>
+      </c>
+      <c r="G218" t="n">
+        <v>55.86</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>1955.2</v>
+      </c>
+      <c r="C219" t="n">
+        <v>1955.2</v>
+      </c>
+      <c r="D219" t="n">
+        <v>1955.2</v>
+      </c>
+      <c r="E219" t="n">
+        <v>105748</v>
+      </c>
+      <c r="F219" t="n">
+        <v>63026</v>
+      </c>
+      <c r="G219" t="n">
+        <v>59.6</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>1963.4</v>
+      </c>
+      <c r="C220" t="n">
+        <v>1963.4</v>
+      </c>
+      <c r="D220" t="n">
+        <v>1963.4</v>
+      </c>
+      <c r="E220" t="n">
+        <v>116879</v>
+      </c>
+      <c r="F220" t="n">
+        <v>58419</v>
+      </c>
+      <c r="G220" t="n">
+        <v>49.98</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>1991.5</v>
+      </c>
+      <c r="C221" t="n">
+        <v>1991.5</v>
+      </c>
+      <c r="D221" t="n">
+        <v>1991.5</v>
+      </c>
+      <c r="E221" t="n">
+        <v>79461</v>
+      </c>
+      <c r="F221" t="n">
+        <v>36982</v>
+      </c>
+      <c r="G221" t="n">
+        <v>46.54</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>1999.2</v>
+      </c>
+      <c r="C222" t="n">
+        <v>1999.2</v>
+      </c>
+      <c r="D222" t="n">
+        <v>1999.2</v>
+      </c>
+      <c r="E222" t="n">
+        <v>50833</v>
+      </c>
+      <c r="F222" t="n">
+        <v>25748</v>
+      </c>
+      <c r="G222" t="n">
+        <v>50.65</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>2027.5</v>
+      </c>
+      <c r="C223" t="n">
+        <v>2027.5</v>
+      </c>
+      <c r="D223" t="n">
+        <v>2027.5</v>
+      </c>
+      <c r="E223" t="n">
+        <v>86603</v>
+      </c>
+      <c r="F223" t="n">
+        <v>35896</v>
+      </c>
+      <c r="G223" t="n">
+        <v>41.45</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>2088.5</v>
+      </c>
+      <c r="C224" t="n">
+        <v>2088.5</v>
+      </c>
+      <c r="D224" t="n">
+        <v>2088.5</v>
+      </c>
+      <c r="E224" t="n">
+        <v>145881</v>
+      </c>
+      <c r="F224" t="n">
+        <v>57550</v>
+      </c>
+      <c r="G224" t="n">
+        <v>39.45</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>2035.6</v>
+      </c>
+      <c r="C225" t="n">
+        <v>2035.6</v>
+      </c>
+      <c r="D225" t="n">
+        <v>2035.6</v>
+      </c>
+      <c r="E225" t="n">
+        <v>71808</v>
+      </c>
+      <c r="F225" t="n">
+        <v>26914</v>
+      </c>
+      <c r="G225" t="n">
+        <v>37.48</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>2024.7</v>
+      </c>
+      <c r="C226" t="n">
+        <v>2024.7</v>
+      </c>
+      <c r="D226" t="n">
+        <v>2024.7</v>
+      </c>
+      <c r="E226" t="n">
+        <v>57473</v>
+      </c>
+      <c r="F226" t="n">
+        <v>25650</v>
+      </c>
+      <c r="G226" t="n">
+        <v>44.63</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>2036.8</v>
+      </c>
+      <c r="C227" t="n">
+        <v>2036.8</v>
+      </c>
+      <c r="D227" t="n">
+        <v>2036.8</v>
+      </c>
+      <c r="E227" t="n">
+        <v>222062</v>
+      </c>
+      <c r="F227" t="n">
+        <v>62563</v>
+      </c>
+      <c r="G227" t="n">
+        <v>28.17</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>2037.3</v>
+      </c>
+      <c r="C228" t="n">
+        <v>2037.3</v>
+      </c>
+      <c r="D228" t="n">
+        <v>2037.3</v>
+      </c>
+      <c r="E228" t="n">
+        <v>158036</v>
+      </c>
+      <c r="F228" t="n">
+        <v>50017</v>
+      </c>
+      <c r="G228" t="n">
+        <v>31.65</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>2025.4</v>
+      </c>
+      <c r="C229" t="n">
+        <v>2025.4</v>
+      </c>
+      <c r="D229" t="n">
+        <v>2025.4</v>
+      </c>
+      <c r="E229" t="n">
+        <v>201317</v>
+      </c>
+      <c r="F229" t="n">
+        <v>45184</v>
+      </c>
+      <c r="G229" t="n">
+        <v>22.44</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>1987.8</v>
+      </c>
+      <c r="C230" t="n">
+        <v>1987.8</v>
+      </c>
+      <c r="D230" t="n">
+        <v>1987.8</v>
+      </c>
+      <c r="E230" t="n">
+        <v>49426</v>
+      </c>
+      <c r="F230" t="n">
+        <v>19714</v>
+      </c>
+      <c r="G230" t="n">
+        <v>39.89</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>2024.1</v>
+      </c>
+      <c r="C231" t="n">
+        <v>2024.1</v>
+      </c>
+      <c r="D231" t="n">
+        <v>2024.1</v>
+      </c>
+      <c r="E231" t="n">
+        <v>179768</v>
+      </c>
+      <c r="F231" t="n">
+        <v>48913</v>
+      </c>
+      <c r="G231" t="n">
+        <v>27.21</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>2024.1</v>
+      </c>
+      <c r="C232" t="n">
+        <v>2024.1</v>
+      </c>
+      <c r="D232" t="n">
+        <v>2024.1</v>
+      </c>
+      <c r="E232" t="n">
+        <v>179768</v>
+      </c>
+      <c r="F232" t="n">
+        <v>48913</v>
+      </c>
+      <c r="G232" t="n">
+        <v>27.21</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>2226.5</v>
+      </c>
+      <c r="C233" t="n">
+        <v>2226.5</v>
+      </c>
+      <c r="D233" t="n">
+        <v>2226.5</v>
+      </c>
+      <c r="E233" t="n">
+        <v>302113</v>
+      </c>
+      <c r="F233" t="n">
+        <v>122871</v>
+      </c>
+      <c r="G233" t="n">
+        <v>40.67</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>2243.2</v>
+      </c>
+      <c r="C234" t="n">
+        <v>2243.2</v>
+      </c>
+      <c r="D234" t="n">
+        <v>2243.2</v>
+      </c>
+      <c r="E234" t="n">
+        <v>310507</v>
+      </c>
+      <c r="F234" t="n">
+        <v>94825</v>
+      </c>
+      <c r="G234" t="n">
+        <v>30.54</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>2149.9</v>
+      </c>
+      <c r="C235" t="n">
+        <v>2149.9</v>
+      </c>
+      <c r="D235" t="n">
+        <v>2149.9</v>
+      </c>
+      <c r="E235" t="n">
+        <v>153299</v>
+      </c>
+      <c r="F235" t="n">
+        <v>43501</v>
+      </c>
+      <c r="G235" t="n">
+        <v>28.38</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>2064.3</v>
+      </c>
+      <c r="C236" t="n">
+        <v>2064.3</v>
+      </c>
+      <c r="D236" t="n">
+        <v>2064.3</v>
+      </c>
+      <c r="E236" t="n">
+        <v>114485</v>
+      </c>
+      <c r="F236" t="n">
+        <v>33699</v>
+      </c>
+      <c r="G236" t="n">
+        <v>29.44</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>2081.3</v>
+      </c>
+      <c r="C237" t="n">
+        <v>2081.3</v>
+      </c>
+      <c r="D237" t="n">
+        <v>2081.3</v>
+      </c>
+      <c r="E237" t="n">
+        <v>64892</v>
+      </c>
+      <c r="F237" t="n">
+        <v>26695</v>
+      </c>
+      <c r="G237" t="n">
+        <v>41.14</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>2030.5</v>
+      </c>
+      <c r="C238" t="n">
+        <v>2030.5</v>
+      </c>
+      <c r="D238" t="n">
+        <v>2030.5</v>
+      </c>
+      <c r="E238" t="n">
+        <v>46918</v>
+      </c>
+      <c r="F238" t="n">
+        <v>23107</v>
+      </c>
+      <c r="G238" t="n">
+        <v>49.25</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>2039.8</v>
+      </c>
+      <c r="C239" t="n">
+        <v>2039.8</v>
+      </c>
+      <c r="D239" t="n">
+        <v>2039.8</v>
+      </c>
+      <c r="E239" t="n">
+        <v>55625</v>
+      </c>
+      <c r="F239" t="n">
+        <v>19253</v>
+      </c>
+      <c r="G239" t="n">
+        <v>34.61</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>2076.4</v>
+      </c>
+      <c r="C240" t="n">
+        <v>2076.4</v>
+      </c>
+      <c r="D240" t="n">
+        <v>2076.4</v>
+      </c>
+      <c r="E240" t="n">
+        <v>45375</v>
+      </c>
+      <c r="F240" t="n">
+        <v>20377</v>
+      </c>
+      <c r="G240" t="n">
+        <v>44.91</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>2041.4</v>
+      </c>
+      <c r="C241" t="n">
+        <v>2041.4</v>
+      </c>
+      <c r="D241" t="n">
+        <v>2041.4</v>
+      </c>
+      <c r="E241" t="n">
+        <v>52141</v>
+      </c>
+      <c r="F241" t="n">
+        <v>21577</v>
+      </c>
+      <c r="G241" t="n">
+        <v>41.38</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>2122.4</v>
+      </c>
+      <c r="C242" t="n">
+        <v>2122.4</v>
+      </c>
+      <c r="D242" t="n">
+        <v>2122.4</v>
+      </c>
+      <c r="E242" t="n">
+        <v>74795</v>
+      </c>
+      <c r="F242" t="n">
+        <v>31479</v>
+      </c>
+      <c r="G242" t="n">
+        <v>42.09</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>2439.1</v>
+      </c>
+      <c r="C243" t="n">
+        <v>2439.1</v>
+      </c>
+      <c r="D243" t="n">
+        <v>2439.1</v>
+      </c>
+      <c r="E243" t="n">
+        <v>458044</v>
+      </c>
+      <c r="F243" t="n">
+        <v>143026</v>
+      </c>
+      <c r="G243" t="n">
+        <v>31.23</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>2601.2</v>
+      </c>
+      <c r="C244" t="n">
+        <v>2601.2</v>
+      </c>
+      <c r="D244" t="n">
+        <v>2601.2</v>
+      </c>
+      <c r="E244" t="n">
+        <v>218995</v>
+      </c>
+      <c r="F244" t="n">
+        <v>77037</v>
+      </c>
+      <c r="G244" t="n">
+        <v>35.18</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>2452.4</v>
+      </c>
+      <c r="C245" t="n">
+        <v>2452.4</v>
+      </c>
+      <c r="D245" t="n">
+        <v>2452.4</v>
+      </c>
+      <c r="E245" t="n">
+        <v>177590</v>
+      </c>
+      <c r="F245" t="n">
+        <v>68733</v>
+      </c>
+      <c r="G245" t="n">
+        <v>38.7</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>2366.9</v>
+      </c>
+      <c r="C246" t="n">
+        <v>2366.9</v>
+      </c>
+      <c r="D246" t="n">
+        <v>2366.9</v>
+      </c>
+      <c r="E246" t="n">
+        <v>75624</v>
+      </c>
+      <c r="F246" t="n">
+        <v>26056</v>
+      </c>
+      <c r="G246" t="n">
+        <v>34.45</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>2498.1</v>
+      </c>
+      <c r="C247" t="n">
+        <v>2498.1</v>
+      </c>
+      <c r="D247" t="n">
+        <v>2498.1</v>
+      </c>
+      <c r="E247" t="n">
+        <v>203107</v>
+      </c>
+      <c r="F247" t="n">
+        <v>44047</v>
+      </c>
+      <c r="G247" t="n">
+        <v>21.69</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>2634.4</v>
+      </c>
+      <c r="C248" t="n">
+        <v>2634.4</v>
+      </c>
+      <c r="D248" t="n">
+        <v>2634.4</v>
+      </c>
+      <c r="E248" t="n">
+        <v>178763</v>
+      </c>
+      <c r="F248" t="n">
+        <v>58925</v>
+      </c>
+      <c r="G248" t="n">
+        <v>32.96</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>2580.5</v>
+      </c>
+      <c r="C249" t="n">
+        <v>2580.5</v>
+      </c>
+      <c r="D249" t="n">
+        <v>2580.5</v>
+      </c>
+      <c r="E249" t="n">
+        <v>90959</v>
+      </c>
+      <c r="F249" t="n">
+        <v>34711</v>
+      </c>
+      <c r="G249" t="n">
+        <v>38.16</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>2632.8</v>
+      </c>
+      <c r="C250" t="n">
+        <v>2632.8</v>
+      </c>
+      <c r="D250" t="n">
+        <v>2632.8</v>
+      </c>
+      <c r="E250" t="n">
+        <v>100164</v>
+      </c>
+      <c r="F250" t="n">
+        <v>28358</v>
+      </c>
+      <c r="G250" t="n">
+        <v>28.31</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>2550.6</v>
+      </c>
+      <c r="C251" t="n">
+        <v>2550.6</v>
+      </c>
+      <c r="D251" t="n">
+        <v>2550.6</v>
+      </c>
+      <c r="E251" t="n">
+        <v>87937</v>
+      </c>
+      <c r="F251" t="n">
+        <v>44174</v>
+      </c>
+      <c r="G251" t="n">
+        <v>50.23</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>2485.1</v>
+      </c>
+      <c r="C252" t="n">
+        <v>2485.1</v>
+      </c>
+      <c r="D252" t="n">
+        <v>2485.1</v>
+      </c>
+      <c r="E252" t="n">
+        <v>98736</v>
+      </c>
+      <c r="F252" t="n">
+        <v>37904</v>
+      </c>
+      <c r="G252" t="n">
+        <v>38.39</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>2582.8</v>
+      </c>
+      <c r="C253" t="n">
+        <v>2582.8</v>
+      </c>
+      <c r="D253" t="n">
+        <v>2582.8</v>
+      </c>
+      <c r="E253" t="n">
+        <v>158022</v>
+      </c>
+      <c r="F253" t="n">
+        <v>47279</v>
+      </c>
+      <c r="G253" t="n">
+        <v>29.92</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>2556.9</v>
+      </c>
+      <c r="C254" t="n">
+        <v>2556.9</v>
+      </c>
+      <c r="D254" t="n">
+        <v>2556.9</v>
+      </c>
+      <c r="E254" t="n">
+        <v>67959</v>
+      </c>
+      <c r="F254" t="n">
+        <v>21571</v>
+      </c>
+      <c r="G254" t="n">
+        <v>31.74</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>2850.4</v>
+      </c>
+      <c r="C255" t="n">
+        <v>2850.4</v>
+      </c>
+      <c r="D255" t="n">
+        <v>2850.4</v>
+      </c>
+      <c r="E255" t="n">
+        <v>2239301</v>
+      </c>
+      <c r="F255" t="n">
+        <v>339828</v>
+      </c>
+      <c r="G255" t="n">
+        <v>15.18</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>2963.4</v>
+      </c>
+      <c r="C256" t="n">
+        <v>2963.4</v>
+      </c>
+      <c r="D256" t="n">
+        <v>2963.4</v>
+      </c>
+      <c r="E256" t="n">
+        <v>1888814</v>
+      </c>
+      <c r="F256" t="n">
+        <v>236614</v>
+      </c>
+      <c r="G256" t="n">
+        <v>12.53</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>2878.6</v>
+      </c>
+      <c r="C257" t="n">
+        <v>2878.6</v>
+      </c>
+      <c r="D257" t="n">
+        <v>2878.6</v>
+      </c>
+      <c r="E257" t="n">
+        <v>657086</v>
+      </c>
+      <c r="F257" t="n">
+        <v>127744</v>
+      </c>
+      <c r="G257" t="n">
+        <v>19.44</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>2569.5</v>
+      </c>
+      <c r="C258" t="n">
+        <v>2569.5</v>
+      </c>
+      <c r="D258" t="n">
+        <v>2569.5</v>
+      </c>
+      <c r="E258" t="n">
+        <v>713255</v>
+      </c>
+      <c r="F258" t="n">
+        <v>204884</v>
+      </c>
+      <c r="G258" t="n">
+        <v>28.73</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>3175.6</v>
+      </c>
+      <c r="C259" t="n">
+        <v>3175.6</v>
+      </c>
+      <c r="D259" t="n">
+        <v>3175.6</v>
+      </c>
+      <c r="E259" t="n">
+        <v>62094</v>
+      </c>
+      <c r="F259" t="n">
+        <v>37564</v>
+      </c>
+      <c r="G259" t="n">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>3331.4</v>
+      </c>
+      <c r="C260" t="n">
+        <v>3331.4</v>
+      </c>
+      <c r="D260" t="n">
+        <v>3331.4</v>
+      </c>
+      <c r="E260" t="n">
+        <v>294517</v>
+      </c>
+      <c r="F260" t="n">
+        <v>119385</v>
+      </c>
+      <c r="G260" t="n">
+        <v>40.54</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>3409.3</v>
+      </c>
+      <c r="C261" t="n">
+        <v>3409.3</v>
+      </c>
+      <c r="D261" t="n">
+        <v>3409.3</v>
+      </c>
+      <c r="E261" t="n">
+        <v>140353</v>
+      </c>
+      <c r="F261" t="n">
+        <v>64765</v>
+      </c>
+      <c r="G261" t="n">
+        <v>46.14</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>3578.4</v>
+      </c>
+      <c r="C262" t="n">
+        <v>3578.4</v>
+      </c>
+      <c r="D262" t="n">
+        <v>3578.4</v>
+      </c>
+      <c r="E262" t="n">
+        <v>198175</v>
+      </c>
+      <c r="F262" t="n">
+        <v>109494</v>
+      </c>
+      <c r="G262" t="n">
+        <v>55.25</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>3701.8</v>
+      </c>
+      <c r="C263" t="n">
+        <v>3701.8</v>
+      </c>
+      <c r="D263" t="n">
+        <v>3701.8</v>
+      </c>
+      <c r="E263" t="n">
+        <v>257636</v>
+      </c>
+      <c r="F263" t="n">
+        <v>119673</v>
+      </c>
+      <c r="G263" t="n">
+        <v>46.45</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>3884.7</v>
+      </c>
+      <c r="C264" t="n">
+        <v>3884.7</v>
+      </c>
+      <c r="D264" t="n">
+        <v>3884.7</v>
+      </c>
+      <c r="E264" t="n">
+        <v>228433</v>
+      </c>
+      <c r="F264" t="n">
+        <v>113335</v>
+      </c>
+      <c r="G264" t="n">
+        <v>49.61</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>3951.4</v>
+      </c>
+      <c r="C265" t="n">
+        <v>3951.4</v>
+      </c>
+      <c r="D265" t="n">
+        <v>3951.4</v>
+      </c>
+      <c r="E265" t="n">
+        <v>222973</v>
+      </c>
+      <c r="F265" t="n">
+        <v>96971</v>
+      </c>
+      <c r="G265" t="n">
+        <v>43.49</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>3951.4</v>
+      </c>
+      <c r="C266" t="n">
+        <v>3951.4</v>
+      </c>
+      <c r="D266" t="n">
+        <v>3951.4</v>
+      </c>
+      <c r="E266" t="n">
+        <v>222973</v>
+      </c>
+      <c r="F266" t="n">
+        <v>96971</v>
+      </c>
+      <c r="G266" t="n">
+        <v>43.49</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>3922.4</v>
+      </c>
+      <c r="C267" t="n">
+        <v>3922.4</v>
+      </c>
+      <c r="D267" t="n">
+        <v>3922.4</v>
+      </c>
+      <c r="E267" t="n">
+        <v>313538</v>
+      </c>
+      <c r="F267" t="n">
+        <v>135873</v>
+      </c>
+      <c r="G267" t="n">
+        <v>43.34</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>4118.5</v>
+      </c>
+      <c r="C268" t="n">
+        <v>4118.5</v>
+      </c>
+      <c r="D268" t="n">
+        <v>4118.5</v>
+      </c>
+      <c r="E268" t="n">
+        <v>248727</v>
+      </c>
+      <c r="F268" t="n">
+        <v>115608</v>
+      </c>
+      <c r="G268" t="n">
+        <v>46.48</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>4324.4</v>
+      </c>
+      <c r="C269" t="n">
+        <v>4324.4</v>
+      </c>
+      <c r="D269" t="n">
+        <v>4324.4</v>
+      </c>
+      <c r="E269" t="n">
+        <v>204649</v>
+      </c>
+      <c r="F269" t="n">
+        <v>107467</v>
+      </c>
+      <c r="G269" t="n">
+        <v>52.51</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>4108.2</v>
+      </c>
+      <c r="C270" t="n">
+        <v>4108.2</v>
+      </c>
+      <c r="D270" t="n">
+        <v>4108.2</v>
+      </c>
+      <c r="E270" t="n">
+        <v>450792</v>
+      </c>
+      <c r="F270" t="n">
+        <v>202567</v>
+      </c>
+      <c r="G270" t="n">
+        <v>44.94</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>4313.6</v>
+      </c>
+      <c r="C271" t="n">
+        <v>4313.6</v>
+      </c>
+      <c r="D271" t="n">
+        <v>4313.6</v>
+      </c>
+      <c r="E271" t="n">
+        <v>215019</v>
+      </c>
+      <c r="F271" t="n">
+        <v>111990</v>
+      </c>
+      <c r="G271" t="n">
+        <v>52.08</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>430.3</v>
+      </c>
+      <c r="C272" t="n">
+        <v>430.3</v>
+      </c>
+      <c r="D272" t="n">
+        <v>430.3</v>
+      </c>
+      <c r="E272" t="n">
+        <v>2467251</v>
+      </c>
+      <c r="F272" t="n">
+        <v>1154249</v>
+      </c>
+      <c r="G272" t="n">
+        <v>46.78</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>408.8</v>
+      </c>
+      <c r="C273" t="n">
+        <v>408.8</v>
+      </c>
+      <c r="D273" t="n">
+        <v>408.8</v>
+      </c>
+      <c r="E273" t="n">
+        <v>3491521</v>
+      </c>
+      <c r="F273" t="n">
+        <v>1613232</v>
+      </c>
+      <c r="G273" t="n">
+        <v>46.2</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>388.4</v>
+      </c>
+      <c r="C274" t="n">
+        <v>388.4</v>
+      </c>
+      <c r="D274" t="n">
+        <v>388.4</v>
+      </c>
+      <c r="E274" t="n">
+        <v>1751202</v>
+      </c>
+      <c r="F274" t="n">
+        <v>955572</v>
+      </c>
+      <c r="G274" t="n">
+        <v>54.57</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>369</v>
+      </c>
+      <c r="C275" t="n">
+        <v>369</v>
+      </c>
+      <c r="D275" t="n">
+        <v>369</v>
+      </c>
+      <c r="E275" t="n">
+        <v>220311</v>
+      </c>
+      <c r="F275" t="n">
+        <v>215317</v>
+      </c>
+      <c r="G275" t="n">
+        <v>97.73</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>386.4</v>
+      </c>
+      <c r="C276" t="n">
+        <v>386.4</v>
+      </c>
+      <c r="D276" t="n">
+        <v>386.4</v>
+      </c>
+      <c r="E276" t="n">
+        <v>6228077</v>
+      </c>
+      <c r="F276" t="n">
+        <v>2197288</v>
+      </c>
+      <c r="G276" t="n">
+        <v>35.28</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="C277" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="D277" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="E277" t="n">
+        <v>4301429</v>
+      </c>
+      <c r="F277" t="n">
+        <v>1477676</v>
+      </c>
+      <c r="G277" t="n">
+        <v>34.35</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>382.5</v>
+      </c>
+      <c r="C278" t="n">
+        <v>382.5</v>
+      </c>
+      <c r="D278" t="n">
+        <v>382.5</v>
+      </c>
+      <c r="E278" t="n">
+        <v>1386909</v>
+      </c>
+      <c r="F278" t="n">
+        <v>555817</v>
+      </c>
+      <c r="G278" t="n">
+        <v>40.08</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>386.4</v>
+      </c>
+      <c r="C279" t="n">
+        <v>386.4</v>
+      </c>
+      <c r="D279" t="n">
+        <v>386.4</v>
+      </c>
+      <c r="E279" t="n">
+        <v>1236447</v>
+      </c>
+      <c r="F279" t="n">
+        <v>493145</v>
+      </c>
+      <c r="G279" t="n">
+        <v>39.88</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>405.7</v>
+      </c>
+      <c r="C280" t="n">
+        <v>405.7</v>
+      </c>
+      <c r="D280" t="n">
+        <v>405.7</v>
+      </c>
+      <c r="E280" t="n">
+        <v>2392972</v>
+      </c>
+      <c r="F280" t="n">
+        <v>1181927</v>
+      </c>
+      <c r="G280" t="n">
+        <v>49.39</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>425.9</v>
+      </c>
+      <c r="C281" t="n">
+        <v>425.9</v>
+      </c>
+      <c r="D281" t="n">
+        <v>425.9</v>
+      </c>
+      <c r="E281" t="n">
+        <v>558938</v>
+      </c>
+      <c r="F281" t="n">
+        <v>431573</v>
+      </c>
+      <c r="G281" t="n">
+        <v>77.20999999999999</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>447.1</v>
+      </c>
+      <c r="C282" t="n">
+        <v>447.1</v>
+      </c>
+      <c r="D282" t="n">
+        <v>447.1</v>
+      </c>
+      <c r="E282" t="n">
+        <v>3014749</v>
+      </c>
+      <c r="F282" t="n">
+        <v>1408417</v>
+      </c>
+      <c r="G282" t="n">
+        <v>46.72</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>433</v>
+      </c>
+      <c r="C283" t="n">
+        <v>433</v>
+      </c>
+      <c r="D283" t="n">
+        <v>433</v>
+      </c>
+      <c r="E283" t="n">
+        <v>4134531</v>
+      </c>
+      <c r="F283" t="n">
+        <v>1703413</v>
+      </c>
+      <c r="G283" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>418.2</v>
+      </c>
+      <c r="C284" t="n">
+        <v>418.2</v>
+      </c>
+      <c r="D284" t="n">
+        <v>418.2</v>
+      </c>
+      <c r="E284" t="n">
+        <v>1672183</v>
+      </c>
+      <c r="F284" t="n">
+        <v>785289</v>
+      </c>
+      <c r="G284" t="n">
+        <v>46.96</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>412.3</v>
+      </c>
+      <c r="C285" t="n">
+        <v>412.3</v>
+      </c>
+      <c r="D285" t="n">
+        <v>412.3</v>
+      </c>
+      <c r="E285" t="n">
+        <v>1439517</v>
+      </c>
+      <c r="F285" t="n">
+        <v>775347</v>
+      </c>
+      <c r="G285" t="n">
+        <v>53.86</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>412.3</v>
+      </c>
+      <c r="C286" t="n">
+        <v>412.3</v>
+      </c>
+      <c r="D286" t="n">
+        <v>412.3</v>
+      </c>
+      <c r="E286" t="n">
+        <v>1439517</v>
+      </c>
+      <c r="F286" t="n">
+        <v>775347</v>
+      </c>
+      <c r="G286" t="n">
+        <v>53.86</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>395.4</v>
+      </c>
+      <c r="C287" t="n">
+        <v>395.4</v>
+      </c>
+      <c r="D287" t="n">
+        <v>395.4</v>
+      </c>
+      <c r="E287" t="n">
+        <v>1549018</v>
+      </c>
+      <c r="F287" t="n">
+        <v>559735</v>
+      </c>
+      <c r="G287" t="n">
+        <v>36.13</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>396.3</v>
+      </c>
+      <c r="C288" t="n">
+        <v>396.3</v>
+      </c>
+      <c r="D288" t="n">
+        <v>396.3</v>
+      </c>
+      <c r="E288" t="n">
+        <v>986293</v>
+      </c>
+      <c r="F288" t="n">
+        <v>428843</v>
+      </c>
+      <c r="G288" t="n">
+        <v>43.48</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>402.7</v>
+      </c>
+      <c r="C289" t="n">
+        <v>402.7</v>
+      </c>
+      <c r="D289" t="n">
+        <v>402.7</v>
+      </c>
+      <c r="E289" t="n">
+        <v>898114</v>
+      </c>
+      <c r="F289" t="n">
+        <v>352229</v>
+      </c>
+      <c r="G289" t="n">
+        <v>39.22</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>388.2</v>
+      </c>
+      <c r="C290" t="n">
+        <v>388.2</v>
+      </c>
+      <c r="D290" t="n">
+        <v>388.2</v>
+      </c>
+      <c r="E290" t="n">
+        <v>1408128</v>
+      </c>
+      <c r="F290" t="n">
+        <v>669818</v>
+      </c>
+      <c r="G290" t="n">
+        <v>47.57</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>382</v>
+      </c>
+      <c r="C291" t="n">
+        <v>382</v>
+      </c>
+      <c r="D291" t="n">
+        <v>382</v>
+      </c>
+      <c r="E291" t="n">
+        <v>1728129</v>
+      </c>
+      <c r="F291" t="n">
+        <v>837998</v>
+      </c>
+      <c r="G291" t="n">
+        <v>48.49</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>381.7</v>
+      </c>
+      <c r="C292" t="n">
+        <v>381.7</v>
+      </c>
+      <c r="D292" t="n">
+        <v>381.7</v>
+      </c>
+      <c r="E292" t="n">
+        <v>1092285</v>
+      </c>
+      <c r="F292" t="n">
+        <v>510747</v>
+      </c>
+      <c r="G292" t="n">
+        <v>46.76</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>371.3</v>
+      </c>
+      <c r="C293" t="n">
+        <v>371.3</v>
+      </c>
+      <c r="D293" t="n">
+        <v>371.3</v>
+      </c>
+      <c r="E293" t="n">
+        <v>688160</v>
+      </c>
+      <c r="F293" t="n">
+        <v>359554</v>
+      </c>
+      <c r="G293" t="n">
+        <v>52.25</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>378.8</v>
+      </c>
+      <c r="C294" t="n">
+        <v>378.8</v>
+      </c>
+      <c r="D294" t="n">
+        <v>378.8</v>
+      </c>
+      <c r="E294" t="n">
+        <v>1701866</v>
+      </c>
+      <c r="F294" t="n">
+        <v>652268</v>
+      </c>
+      <c r="G294" t="n">
+        <v>38.33</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>397.7</v>
+      </c>
+      <c r="C295" t="n">
+        <v>397.7</v>
+      </c>
+      <c r="D295" t="n">
+        <v>397.7</v>
+      </c>
+      <c r="E295" t="n">
+        <v>1393285</v>
+      </c>
+      <c r="F295" t="n">
+        <v>714129</v>
+      </c>
+      <c r="G295" t="n">
+        <v>51.26</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>397.9</v>
+      </c>
+      <c r="C296" t="n">
+        <v>397.9</v>
+      </c>
+      <c r="D296" t="n">
+        <v>397.9</v>
+      </c>
+      <c r="E296" t="n">
+        <v>1071224</v>
+      </c>
+      <c r="F296" t="n">
+        <v>489874</v>
+      </c>
+      <c r="G296" t="n">
+        <v>45.73</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>386.95</v>
+      </c>
+      <c r="C297" t="n">
+        <v>386.95</v>
+      </c>
+      <c r="D297" t="n">
+        <v>386.95</v>
+      </c>
+      <c r="E297" t="n">
+        <v>751831</v>
+      </c>
+      <c r="F297" t="n">
+        <v>399478</v>
+      </c>
+      <c r="G297" t="n">
+        <v>53.13</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>394.6</v>
+      </c>
+      <c r="C298" t="n">
+        <v>394.6</v>
+      </c>
+      <c r="D298" t="n">
+        <v>394.6</v>
+      </c>
+      <c r="E298" t="n">
+        <v>1171985</v>
+      </c>
+      <c r="F298" t="n">
+        <v>501277</v>
+      </c>
+      <c r="G298" t="n">
+        <v>42.77</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>410.9</v>
+      </c>
+      <c r="C299" t="n">
+        <v>410.9</v>
+      </c>
+      <c r="D299" t="n">
+        <v>410.9</v>
+      </c>
+      <c r="E299" t="n">
+        <v>2148139</v>
+      </c>
+      <c r="F299" t="n">
+        <v>937659</v>
+      </c>
+      <c r="G299" t="n">
+        <v>43.65</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>423.5</v>
+      </c>
+      <c r="C300" t="n">
+        <v>423.5</v>
+      </c>
+      <c r="D300" t="n">
+        <v>423.5</v>
+      </c>
+      <c r="E300" t="n">
+        <v>1838322</v>
+      </c>
+      <c r="F300" t="n">
+        <v>823025</v>
+      </c>
+      <c r="G300" t="n">
+        <v>44.77</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>404.95</v>
+      </c>
+      <c r="C301" t="n">
+        <v>404.95</v>
+      </c>
+      <c r="D301" t="n">
+        <v>404.95</v>
+      </c>
+      <c r="E301" t="n">
+        <v>2414292</v>
+      </c>
+      <c r="F301" t="n">
+        <v>1083588</v>
+      </c>
+      <c r="G301" t="n">
+        <v>44.88</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>425.15</v>
+      </c>
+      <c r="C302" t="n">
+        <v>425.15</v>
+      </c>
+      <c r="D302" t="n">
+        <v>425.15</v>
+      </c>
+      <c r="E302" t="n">
+        <v>2515611</v>
+      </c>
+      <c r="F302" t="n">
+        <v>1389393</v>
+      </c>
+      <c r="G302" t="n">
+        <v>55.23</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>446.4</v>
+      </c>
+      <c r="C303" t="n">
+        <v>446.4</v>
+      </c>
+      <c r="D303" t="n">
+        <v>446.4</v>
+      </c>
+      <c r="E303" t="n">
+        <v>2758582</v>
+      </c>
+      <c r="F303" t="n">
+        <v>1266059</v>
+      </c>
+      <c r="G303" t="n">
+        <v>45.9</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>468.7</v>
+      </c>
+      <c r="C304" t="n">
+        <v>468.7</v>
+      </c>
+      <c r="D304" t="n">
+        <v>468.7</v>
+      </c>
+      <c r="E304" t="n">
+        <v>121637</v>
+      </c>
+      <c r="F304" t="n">
+        <v>121636</v>
+      </c>
+      <c r="G304" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>492.1</v>
+      </c>
+      <c r="C305" t="n">
+        <v>492.1</v>
+      </c>
+      <c r="D305" t="n">
+        <v>492.1</v>
+      </c>
+      <c r="E305" t="n">
+        <v>114305</v>
+      </c>
+      <c r="F305" t="n">
+        <v>114305</v>
+      </c>
+      <c r="G305" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>516.7</v>
+      </c>
+      <c r="C306" t="n">
+        <v>516.7</v>
+      </c>
+      <c r="D306" t="n">
+        <v>516.7</v>
+      </c>
+      <c r="E306" t="n">
+        <v>7140040</v>
+      </c>
+      <c r="F306" t="n">
+        <v>2730593</v>
+      </c>
+      <c r="G306" t="n">
+        <v>38.24</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>542.5</v>
+      </c>
+      <c r="C307" t="n">
+        <v>542.5</v>
+      </c>
+      <c r="D307" t="n">
+        <v>542.5</v>
+      </c>
+      <c r="E307" t="n">
+        <v>429556</v>
+      </c>
+      <c r="F307" t="n">
+        <v>359916</v>
+      </c>
+      <c r="G307" t="n">
+        <v>83.79000000000001</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>515.4</v>
+      </c>
+      <c r="C308" t="n">
+        <v>515.4</v>
+      </c>
+      <c r="D308" t="n">
+        <v>515.4</v>
+      </c>
+      <c r="E308" t="n">
+        <v>5885813</v>
+      </c>
+      <c r="F308" t="n">
+        <v>2431429</v>
+      </c>
+      <c r="G308" t="n">
+        <v>41.31</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>491.45</v>
+      </c>
+      <c r="C309" t="n">
+        <v>491.45</v>
+      </c>
+      <c r="D309" t="n">
+        <v>491.45</v>
+      </c>
+      <c r="E309" t="n">
+        <v>5202149</v>
+      </c>
+      <c r="F309" t="n">
+        <v>1793275</v>
+      </c>
+      <c r="G309" t="n">
+        <v>34.47</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>492.55</v>
+      </c>
+      <c r="C310" t="n">
+        <v>492.55</v>
+      </c>
+      <c r="D310" t="n">
+        <v>492.55</v>
+      </c>
+      <c r="E310" t="n">
+        <v>1788213</v>
+      </c>
+      <c r="F310" t="n">
+        <v>698634</v>
+      </c>
+      <c r="G310" t="n">
+        <v>39.07</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>517.15</v>
+      </c>
+      <c r="C311" t="n">
+        <v>517.15</v>
+      </c>
+      <c r="D311" t="n">
+        <v>517.15</v>
+      </c>
+      <c r="E311" t="n">
+        <v>217316</v>
+      </c>
+      <c r="F311" t="n">
+        <v>212691</v>
+      </c>
+      <c r="G311" t="n">
+        <v>97.87</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>543</v>
+      </c>
+      <c r="C312" t="n">
+        <v>543</v>
+      </c>
+      <c r="D312" t="n">
+        <v>543</v>
+      </c>
+      <c r="E312" t="n">
+        <v>539520</v>
+      </c>
+      <c r="F312" t="n">
+        <v>356236</v>
+      </c>
+      <c r="G312" t="n">
+        <v>66.03</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>570.15</v>
+      </c>
+      <c r="C313" t="n">
+        <v>570.15</v>
+      </c>
+      <c r="D313" t="n">
+        <v>570.15</v>
+      </c>
+      <c r="E313" t="n">
+        <v>2968119</v>
+      </c>
+      <c r="F313" t="n">
+        <v>1241421</v>
+      </c>
+      <c r="G313" t="n">
+        <v>41.83</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>598.65</v>
+      </c>
+      <c r="C314" t="n">
+        <v>598.65</v>
+      </c>
+      <c r="D314" t="n">
+        <v>598.65</v>
+      </c>
+      <c r="E314" t="n">
+        <v>2619172</v>
+      </c>
+      <c r="F314" t="n">
+        <v>1002999</v>
+      </c>
+      <c r="G314" t="n">
+        <v>38.29</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>605.7</v>
+      </c>
+      <c r="C315" t="n">
+        <v>605.7</v>
+      </c>
+      <c r="D315" t="n">
+        <v>605.7</v>
+      </c>
+      <c r="E315" t="n">
+        <v>3029968</v>
+      </c>
+      <c r="F315" t="n">
+        <v>1078350</v>
+      </c>
+      <c r="G315" t="n">
+        <v>35.59</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>575.45</v>
+      </c>
+      <c r="C316" t="n">
+        <v>575.45</v>
+      </c>
+      <c r="D316" t="n">
+        <v>575.45</v>
+      </c>
+      <c r="E316" t="n">
+        <v>2106565</v>
+      </c>
+      <c r="F316" t="n">
+        <v>1042804</v>
+      </c>
+      <c r="G316" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="B138" t="n">
+      <c r="B317" t="n">
         <v>602.8</v>
       </c>
-      <c r="C138" t="n">
+      <c r="C317" t="n">
+        <v>602.8</v>
+      </c>
+      <c r="D317" t="n">
+        <v>602.8</v>
+      </c>
+      <c r="E317" t="n">
         <v>3378109</v>
       </c>
-      <c r="D138" t="n">
+      <c r="F317" t="n">
         <v>1203783</v>
       </c>
-      <c r="E138" t="n">
+      <c r="G317" t="n">
         <v>35.63</v>
       </c>
     </row>
